--- a/data/ATH PRICE LIST - MAIN.xlsx
+++ b/data/ATH PRICE LIST - MAIN.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B43EC7A-BB6B-47FB-8BF1-B848382571A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F426EEBB-C8FE-4EEB-ACBD-F56144BDDD43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12,7 +12,7 @@
     <sheet name="HYGIENE" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5347" uniqueCount="2290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5346" uniqueCount="2290">
   <si>
     <t>ITEM CODE</t>
   </si>
@@ -7137,7 +7137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7323,7 +7323,6 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -7332,6 +7331,51 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="35">
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;£&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF003459"/>
+        <name val="Open Sans"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="&quot;£&quot;#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD7E2EA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD7E2EA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD7E2EA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD7E2EA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -7785,9 +7829,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="166" formatCode="&quot;£&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;£&quot;#,##0.00"/>
       <border>
         <right style="thin">
           <color rgb="FFD7E2EA"/>
@@ -7882,48 +7923,6 @@
           <color rgb="FFD7E2EA"/>
         </left>
         <right/>
-        <top style="thin">
-          <color rgb="FFD7E2EA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD7E2EA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF003459"/>
-        <name val="Open Sans"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD7E2EA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD7E2EA"/>
-        </right>
         <top style="thin">
           <color rgb="FFD7E2EA"/>
         </top>
@@ -8311,18 +8310,18 @@
     <tableColumn id="5" xr3:uid="{744F3FEB-B2BB-46CD-91BB-9903C93C04A0}" name="ORDER QUANTITY" dataDxfId="26"/>
     <tableColumn id="6" xr3:uid="{BE208337-FC74-4295-B603-877D02E7270C}" name="REMARKS" dataDxfId="25"/>
     <tableColumn id="7" xr3:uid="{B327B6AC-4DA5-4EE3-9FEC-E29879EA401C}" name="COST PRICE" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{D1AE8B80-9F11-4600-87C5-242E31E05413}" name="SALE PRICE" dataDxfId="23">
+    <tableColumn id="8" xr3:uid="{D1AE8B80-9F11-4600-87C5-242E31E05413}" name="SALE PRICE" dataDxfId="1">
       <calculatedColumnFormula>IF(G2&lt;=5,G2*1.6,
 IF(G2&lt;=10,G2*1.55,
-IF(G2&lt;=25,G2*1.45,
+IF(G2&lt;=25,G2*1.5,
 IF(G2&lt;=50,G2*1.4,
-IF(G2&lt;=100,G2*1.35,
-G2*1.333)))))</calculatedColumnFormula>
+IF(G2&lt;=100,G2*1.4,
+G2*1.4)))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{D65348A8-D3C5-406A-80F9-93D15AFF4CE1}" name="MARGIN" dataDxfId="22">
+    <tableColumn id="9" xr3:uid="{D65348A8-D3C5-406A-80F9-93D15AFF4CE1}" name="MARGIN" dataDxfId="23">
       <calculatedColumnFormula>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{5C08FCA1-1C90-40D5-8300-048EB18A879B}" name="REVIEW" dataDxfId="21">
+    <tableColumn id="10" xr3:uid="{5C08FCA1-1C90-40D5-8300-048EB18A879B}" name="REVIEW" dataDxfId="22">
       <calculatedColumnFormula>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8331,7 +8330,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1FFDF47A-E342-422A-B88B-3A1A2E026791}" name="Table4" displayName="Table4" ref="A903:J1135" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1FFDF47A-E342-422A-B88B-3A1A2E026791}" name="Table4" displayName="Table4" ref="A903:J1135" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="A903:J1135" xr:uid="{1FFDF47A-E342-422A-B88B-3A1A2E026791}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{EC083E47-92C1-4608-BB77-63FF75756A56}" name="ITEM CODE"/>
@@ -8340,12 +8339,19 @@
     <tableColumn id="4" xr3:uid="{7C6AE945-693E-421A-9F18-AAE794477761}" name="SUPPLIER"/>
     <tableColumn id="5" xr3:uid="{F720DDC8-0CA5-481C-8C77-9DBD45E005F8}" name="ORDER QUANTITY"/>
     <tableColumn id="6" xr3:uid="{5E5A2EF2-4DF8-4E60-A339-BB4539A8EBA4}" name="REMARKS"/>
-    <tableColumn id="7" xr3:uid="{3E943F4C-FB6A-4F18-B0C1-95576F16AB51}" name="COST PRICE" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{0F77740A-2E8B-4224-BD0B-CC6FA87DAAA1}" name="SALE PRICE" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{78601A2A-BBB6-43B8-9807-DEAA960510F0}" name="MARGIN" dataDxfId="14">
+    <tableColumn id="7" xr3:uid="{3E943F4C-FB6A-4F18-B0C1-95576F16AB51}" name="COST PRICE" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{0F77740A-2E8B-4224-BD0B-CC6FA87DAAA1}" name="SALE PRICE" dataDxfId="0">
+      <calculatedColumnFormula>IF(G904&lt;=5,G904*1.6,
+IF(G904&lt;=10,G904*1.55,
+IF(G904&lt;=25,G904*1.5,
+IF(G904&lt;=50,G904*1.4,
+IF(G904&lt;=100,G904*1.4,
+G904*1.4)))))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{78601A2A-BBB6-43B8-9807-DEAA960510F0}" name="MARGIN" dataDxfId="16">
       <calculatedColumnFormula>(Table4[[#This Row],[SALE PRICE]]-Table4[[#This Row],[COST PRICE]])/Table4[[#This Row],[SALE PRICE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{6B8956C3-29C4-495D-B64A-FAA306125BBF}" name="REVIEW" dataDxfId="13">
+    <tableColumn id="10" xr3:uid="{6B8956C3-29C4-495D-B64A-FAA306125BBF}" name="REVIEW" dataDxfId="15">
       <calculatedColumnFormula>IF(Table4[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8354,17 +8360,17 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3AF7D65F-4EB0-4B92-B2C8-7E263D1FE628}" name="Table2" displayName="Table2" ref="A1:J48" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3AF7D65F-4EB0-4B92-B2C8-7E263D1FE628}" name="Table2" displayName="Table2" ref="A1:J48" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="A1:J48" xr:uid="{3AF7D65F-4EB0-4B92-B2C8-7E263D1FE628}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{14E88C55-5845-4EB3-8BDC-9AAAF5A6F0C3}" name="ITEM CODE" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{57D09E13-81AF-47BC-9D05-99F71786FE5B}" name="PRODUCT NAME" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{F0BEC22F-0FE1-462E-8FBA-2B08E5092A0F}" name="UNIT" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{7CE7802E-9851-4936-B09A-A24190FDD694}" name="SUPPLIER" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{E3150DA9-C6F5-487B-A753-0D104DEFFA86}" name="ORDER QUANTITY" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{D0A961F0-6484-49DF-9B99-78A910D93D24}" name="REMARKS" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{67DDF1CA-3EB9-4DC7-B307-F5C1D764BEE4}" name="COST PRICE" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{0612F545-E962-4829-9D79-CB23C4A0C0D3}" name="SALE PRICE" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{14E88C55-5845-4EB3-8BDC-9AAAF5A6F0C3}" name="ITEM CODE" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{57D09E13-81AF-47BC-9D05-99F71786FE5B}" name="PRODUCT NAME" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{F0BEC22F-0FE1-462E-8FBA-2B08E5092A0F}" name="UNIT" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{7CE7802E-9851-4936-B09A-A24190FDD694}" name="SUPPLIER" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{E3150DA9-C6F5-487B-A753-0D104DEFFA86}" name="ORDER QUANTITY" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{D0A961F0-6484-49DF-9B99-78A910D93D24}" name="REMARKS" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{67DDF1CA-3EB9-4DC7-B307-F5C1D764BEE4}" name="COST PRICE" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{0612F545-E962-4829-9D79-CB23C4A0C0D3}" name="SALE PRICE" dataDxfId="4">
       <calculatedColumnFormula>IF(G2&lt;=5,G2*1.6,
 IF(G2&lt;=10,G2*1.55,
 IF(G2&lt;=25,G2*1.45,
@@ -8372,10 +8378,10 @@
 IF(G2&lt;=100,G2*1.35,
 G2*1.333)))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{0E33FDEE-1CF7-447B-A1FC-CC7BEF79D4F1}" name="MARGIN" dataDxfId="1">
+    <tableColumn id="9" xr3:uid="{0E33FDEE-1CF7-447B-A1FC-CC7BEF79D4F1}" name="MARGIN" dataDxfId="3">
       <calculatedColumnFormula>(Table2[[#This Row],[SALE PRICE]]-Table2[[#This Row],[COST PRICE]])/Table2[[#This Row],[SALE PRICE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{30BB9253-B37A-4764-A8D9-F4E102099A98}" name="REVIEW" dataDxfId="0">
+    <tableColumn id="10" xr3:uid="{30BB9253-B37A-4764-A8D9-F4E102099A98}" name="REVIEW" dataDxfId="2">
       <calculatedColumnFormula>IF(Table2[[#This Row],[MARGIN]]&gt;25, "REVIEW", "OK")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8772,7 +8778,15 @@
       <c r="G2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="14"/>
+      <c r="H2" s="14" t="e">
+        <f t="shared" ref="H2:H65" si="0">IF(G2&lt;=5,G2*1.6,
+IF(G2&lt;=10,G2*1.55,
+IF(G2&lt;=25,G2*1.5,
+IF(G2&lt;=50,G2*1.4,
+IF(G2&lt;=100,G2*1.4,
+G2*1.4)))))</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="I2" s="24"/>
       <c r="J2" s="24"/>
     </row>
@@ -8799,12 +8813,7 @@
         <v>8.51</v>
       </c>
       <c r="H3" s="51">
-        <f t="shared" ref="H3:H69" si="0">IF(G3&lt;=5,G3*1.6,
-IF(G3&lt;=10,G3*1.55,
-IF(G3&lt;=25,G3*1.45,
-IF(G3&lt;=50,G3*1.4,
-IF(G3&lt;=100,G3*1.35,
-G3*1.333)))))</f>
+        <f t="shared" si="0"/>
         <v>13.1905</v>
       </c>
       <c r="I3" s="32">
@@ -8968,11 +8977,11 @@
       </c>
       <c r="H8" s="52">
         <f t="shared" si="0"/>
-        <v>32.277000000000001</v>
+        <v>33.39</v>
       </c>
       <c r="I8" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J8" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9003,11 +9012,11 @@
       </c>
       <c r="H9" s="51">
         <f t="shared" si="0"/>
-        <v>18.27</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="I9" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J9" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9038,11 +9047,11 @@
       </c>
       <c r="H10" s="52">
         <f t="shared" si="0"/>
-        <v>14.79</v>
+        <v>15.299999999999999</v>
       </c>
       <c r="I10" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J10" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9067,11 +9076,11 @@
       </c>
       <c r="H11" s="51">
         <f t="shared" si="0"/>
-        <v>22.170499999999997</v>
+        <v>22.934999999999999</v>
       </c>
       <c r="I11" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J11" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9102,11 +9111,11 @@
       </c>
       <c r="H12" s="52">
         <f t="shared" si="0"/>
-        <v>14.79</v>
+        <v>15.299999999999999</v>
       </c>
       <c r="I12" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J12" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9137,11 +9146,11 @@
       </c>
       <c r="H13" s="51">
         <f t="shared" si="0"/>
-        <v>15.66</v>
+        <v>16.200000000000003</v>
       </c>
       <c r="I13" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333343</v>
       </c>
       <c r="J13" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9201,11 +9210,11 @@
       </c>
       <c r="H15" s="51">
         <f t="shared" si="0"/>
-        <v>15.66</v>
+        <v>16.200000000000003</v>
       </c>
       <c r="I15" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333343</v>
       </c>
       <c r="J15" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9230,11 +9239,11 @@
       </c>
       <c r="H16" s="52">
         <f t="shared" si="0"/>
-        <v>19.574999999999999</v>
+        <v>20.25</v>
       </c>
       <c r="I16" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J16" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9265,11 +9274,11 @@
       </c>
       <c r="H17" s="51">
         <f t="shared" si="0"/>
-        <v>18.356999999999999</v>
+        <v>18.990000000000002</v>
       </c>
       <c r="I17" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J17" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9300,11 +9309,11 @@
       </c>
       <c r="H18" s="52">
         <f t="shared" si="0"/>
-        <v>16.094999999999999</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="I18" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J18" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9335,11 +9344,11 @@
       </c>
       <c r="H19" s="51">
         <f t="shared" si="0"/>
-        <v>21.735499999999998</v>
+        <v>22.484999999999999</v>
       </c>
       <c r="I19" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J19" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9370,11 +9379,11 @@
       </c>
       <c r="H20" s="52">
         <f t="shared" si="0"/>
-        <v>19.647500000000001</v>
+        <v>20.325000000000003</v>
       </c>
       <c r="I20" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J20" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9471,7 +9480,10 @@
       <c r="G23" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H23" s="53"/>
+      <c r="H23" s="53" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I23" s="24"/>
       <c r="J23" s="24"/>
     </row>
@@ -9499,11 +9511,11 @@
       </c>
       <c r="H24" s="52">
         <f t="shared" si="0"/>
-        <v>16.515499999999999</v>
+        <v>17.085000000000001</v>
       </c>
       <c r="I24" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J24" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9534,11 +9546,11 @@
       </c>
       <c r="H25" s="51">
         <f t="shared" si="0"/>
-        <v>15.645499999999998</v>
+        <v>16.184999999999999</v>
       </c>
       <c r="I25" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J25" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9569,11 +9581,11 @@
       </c>
       <c r="H26" s="52">
         <f t="shared" si="0"/>
-        <v>16.515499999999999</v>
+        <v>17.085000000000001</v>
       </c>
       <c r="I26" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J26" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9604,11 +9616,11 @@
       </c>
       <c r="H27" s="51">
         <f t="shared" si="0"/>
-        <v>34.785499999999999</v>
+        <v>35.984999999999999</v>
       </c>
       <c r="I27" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J27" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9639,11 +9651,11 @@
       </c>
       <c r="H28" s="52">
         <f t="shared" si="0"/>
-        <v>17.907499999999999</v>
+        <v>18.524999999999999</v>
       </c>
       <c r="I28" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J28" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9709,11 +9721,11 @@
       </c>
       <c r="H30" s="52">
         <f t="shared" si="0"/>
-        <v>18.255499999999998</v>
+        <v>18.884999999999998</v>
       </c>
       <c r="I30" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.3103448275862068</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="J30" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9744,11 +9756,11 @@
       </c>
       <c r="H31" s="51">
         <f t="shared" si="0"/>
-        <v>18.255499999999998</v>
+        <v>18.884999999999998</v>
       </c>
       <c r="I31" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.3103448275862068</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="J31" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9779,11 +9791,11 @@
       </c>
       <c r="H32" s="52">
         <f t="shared" si="0"/>
-        <v>29.406000000000002</v>
+        <v>30.42</v>
       </c>
       <c r="I32" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J32" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9807,17 +9819,12 @@
         <v>20.28</v>
       </c>
       <c r="H33" s="51">
-        <f>IF(G33&lt;=5,G33*1.6,
-IF(G33&lt;=10,G33*1.55,
-IF(G33&lt;=25,G33*1.45,
-IF(G33&lt;=50,G33*1.4,
-IF(G33&lt;=100,G33*1.35,
-G33*1.333)))))</f>
-        <v>29.406000000000002</v>
+        <f t="shared" si="0"/>
+        <v>30.42</v>
       </c>
       <c r="I33" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J33" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9848,11 +9855,11 @@
       </c>
       <c r="H34" s="52">
         <f t="shared" si="0"/>
-        <v>21.2135</v>
+        <v>21.945</v>
       </c>
       <c r="I34" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J34" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9883,11 +9890,11 @@
       </c>
       <c r="H35" s="51">
         <f t="shared" si="0"/>
-        <v>16.515499999999999</v>
+        <v>17.085000000000001</v>
       </c>
       <c r="I35" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J35" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9918,11 +9925,11 @@
       </c>
       <c r="H36" s="52">
         <f t="shared" si="0"/>
-        <v>21.2135</v>
+        <v>21.945</v>
       </c>
       <c r="I36" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J36" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9953,11 +9960,11 @@
       </c>
       <c r="H37" s="51">
         <f t="shared" si="0"/>
-        <v>16.471999999999998</v>
+        <v>17.04</v>
       </c>
       <c r="I37" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J37" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -9981,12 +9988,7 @@
         <v>2.99</v>
       </c>
       <c r="H38" s="52">
-        <f>IF(G38&lt;=5,G38*1.6,
-IF(G38&lt;=10,G38*1.55,
-IF(G38&lt;=25,G38*1.45,
-IF(G38&lt;=50,G38*1.4,
-IF(G38&lt;=100,G38*1.35,
-G38*1.333)))))</f>
+        <f t="shared" si="0"/>
         <v>4.7840000000000007</v>
       </c>
       <c r="I38" s="34">
@@ -10015,12 +10017,7 @@
         <v>6.99</v>
       </c>
       <c r="H39" s="51">
-        <f>IF(G39&lt;=5,G39*1.6,
-IF(G39&lt;=10,G39*1.55,
-IF(G39&lt;=25,G39*1.45,
-IF(G39&lt;=50,G39*1.4,
-IF(G39&lt;=100,G39*1.35,
-G39*1.333)))))</f>
+        <f t="shared" si="0"/>
         <v>10.8345</v>
       </c>
       <c r="I39" s="34">
@@ -10049,17 +10046,12 @@
         <v>14.99</v>
       </c>
       <c r="H40" s="52">
-        <f>IF(G40&lt;=5,G40*1.6,
-IF(G40&lt;=10,G40*1.55,
-IF(G40&lt;=25,G40*1.45,
-IF(G40&lt;=50,G40*1.4,
-IF(G40&lt;=100,G40*1.35,
-G40*1.333)))))</f>
-        <v>21.735499999999998</v>
+        <f t="shared" si="0"/>
+        <v>22.484999999999999</v>
       </c>
       <c r="I40" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J40" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -10086,7 +10078,10 @@
       <c r="G41" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H41" s="53"/>
+      <c r="H41" s="53" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I41" s="24"/>
       <c r="J41" s="24"/>
     </row>
@@ -10219,11 +10214,11 @@
       </c>
       <c r="H45" s="51">
         <f t="shared" si="0"/>
-        <v>27.912499999999998</v>
+        <v>28.875</v>
       </c>
       <c r="I45" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J45" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -10254,11 +10249,11 @@
       </c>
       <c r="H46" s="52">
         <f t="shared" si="0"/>
-        <v>21.387499999999999</v>
+        <v>22.125</v>
       </c>
       <c r="I46" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J46" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -10359,11 +10354,11 @@
       </c>
       <c r="H49" s="51">
         <f t="shared" si="0"/>
-        <v>17.037499999999998</v>
+        <v>17.625</v>
       </c>
       <c r="I49" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.3103448275862068</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J49" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -10394,11 +10389,11 @@
       </c>
       <c r="H50" s="52">
         <f t="shared" si="0"/>
-        <v>34.785499999999999</v>
+        <v>35.984999999999999</v>
       </c>
       <c r="I50" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J50" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -10429,11 +10424,11 @@
       </c>
       <c r="H51" s="51">
         <f t="shared" si="0"/>
-        <v>27.1005</v>
+        <v>28.035000000000004</v>
       </c>
       <c r="I51" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J51" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -10495,7 +10490,10 @@
       <c r="G53" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H53" s="53"/>
+      <c r="H53" s="53" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I53" s="24"/>
       <c r="J53" s="24"/>
     </row>
@@ -10523,15 +10521,15 @@
       </c>
       <c r="H54" s="52">
         <f t="shared" si="0"/>
-        <v>158.21376999999998</v>
+        <v>166.166</v>
       </c>
       <c r="I54" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.24981245311327824</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J54" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
-        <v>REVIEW</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -10558,11 +10556,11 @@
       </c>
       <c r="H55" s="51">
         <f t="shared" si="0"/>
-        <v>23.910499999999995</v>
+        <v>24.734999999999999</v>
       </c>
       <c r="I55" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J55" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -10593,11 +10591,11 @@
       </c>
       <c r="H56" s="52">
         <f t="shared" si="0"/>
-        <v>106.6365</v>
+        <v>110.58599999999998</v>
       </c>
       <c r="I56" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.2592592592592593</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J56" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -10628,11 +10626,11 @@
       </c>
       <c r="H57" s="51">
         <f t="shared" si="0"/>
-        <v>15.935499999999999</v>
+        <v>16.484999999999999</v>
       </c>
       <c r="I57" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J57" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -10733,11 +10731,11 @@
       </c>
       <c r="H60" s="52">
         <f t="shared" si="0"/>
-        <v>24.635499999999997</v>
+        <v>25.484999999999999</v>
       </c>
       <c r="I60" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J60" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -10803,11 +10801,11 @@
       </c>
       <c r="H62" s="52">
         <f t="shared" si="0"/>
-        <v>25.360499999999998</v>
+        <v>26.234999999999999</v>
       </c>
       <c r="I62" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J62" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -10936,7 +10934,12 @@
         <v>6.59</v>
       </c>
       <c r="H66" s="52">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H66:H129" si="1">IF(G66&lt;=5,G66*1.6,
+IF(G66&lt;=10,G66*1.55,
+IF(G66&lt;=25,G66*1.5,
+IF(G66&lt;=50,G66*1.4,
+IF(G66&lt;=100,G66*1.4,
+G66*1.4)))))</f>
         <v>10.214499999999999</v>
       </c>
       <c r="I66" s="34">
@@ -10971,7 +10974,7 @@
         <v>9.99</v>
       </c>
       <c r="H67" s="51">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15.484500000000001</v>
       </c>
       <c r="I67" s="32">
@@ -11003,7 +11006,10 @@
       <c r="G68" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H68" s="53"/>
+      <c r="H68" s="53" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I68" s="24"/>
       <c r="J68" s="24"/>
     </row>
@@ -11030,7 +11036,7 @@
         <v>8.89</v>
       </c>
       <c r="H69" s="51">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13.779500000000001</v>
       </c>
       <c r="I69" s="32">
@@ -11065,17 +11071,12 @@
         <v>16.989999999999998</v>
       </c>
       <c r="H70" s="52">
-        <f t="shared" ref="H70:H133" si="1">IF(G70&lt;=5,G70*1.6,
-IF(G70&lt;=10,G70*1.55,
-IF(G70&lt;=25,G70*1.45,
-IF(G70&lt;=50,G70*1.4,
-IF(G70&lt;=100,G70*1.35,
-G70*1.333)))))</f>
-        <v>24.635499999999997</v>
+        <f t="shared" si="1"/>
+        <v>25.484999999999999</v>
       </c>
       <c r="I70" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J70" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -11141,11 +11142,11 @@
       </c>
       <c r="H72" s="52">
         <f t="shared" si="1"/>
-        <v>33.335499999999996</v>
+        <v>34.484999999999999</v>
       </c>
       <c r="I72" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J72" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -11176,11 +11177,11 @@
       </c>
       <c r="H73" s="51">
         <f t="shared" si="1"/>
-        <v>16.805499999999999</v>
+        <v>17.384999999999998</v>
       </c>
       <c r="I73" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="J73" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -11211,11 +11212,11 @@
       </c>
       <c r="H74" s="52">
         <f t="shared" si="1"/>
-        <v>16.805499999999999</v>
+        <v>17.384999999999998</v>
       </c>
       <c r="I74" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="J74" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -11456,11 +11457,11 @@
       </c>
       <c r="H81" s="51">
         <f t="shared" si="1"/>
-        <v>15.2105</v>
+        <v>15.734999999999999</v>
       </c>
       <c r="I81" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J81" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -11491,11 +11492,11 @@
       </c>
       <c r="H82" s="52">
         <f t="shared" si="1"/>
-        <v>14.920499999999999</v>
+        <v>15.434999999999999</v>
       </c>
       <c r="I82" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J82" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -11586,7 +11587,10 @@
       <c r="G85" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H85" s="53"/>
+      <c r="H85" s="53" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I85" s="24"/>
       <c r="J85" s="24"/>
     </row>
@@ -11649,11 +11653,11 @@
       </c>
       <c r="H87" s="51">
         <f t="shared" si="1"/>
-        <v>17.095499999999998</v>
+        <v>17.684999999999999</v>
       </c>
       <c r="I87" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J87" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -11684,11 +11688,11 @@
       </c>
       <c r="H88" s="52">
         <f t="shared" si="1"/>
-        <v>23.185500000000001</v>
+        <v>23.984999999999999</v>
       </c>
       <c r="I88" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J88" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -11754,11 +11758,11 @@
       </c>
       <c r="H90" s="52">
         <f t="shared" si="1"/>
-        <v>24.635499999999997</v>
+        <v>25.484999999999999</v>
       </c>
       <c r="I90" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J90" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -11789,11 +11793,11 @@
       </c>
       <c r="H91" s="51">
         <f t="shared" si="1"/>
-        <v>24.635499999999997</v>
+        <v>25.484999999999999</v>
       </c>
       <c r="I91" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J91" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -11820,7 +11824,10 @@
       <c r="G92" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H92" s="53"/>
+      <c r="H92" s="53" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I92" s="24"/>
       <c r="J92" s="24"/>
     </row>
@@ -11988,11 +11995,11 @@
       </c>
       <c r="H97" s="51">
         <f t="shared" si="1"/>
-        <v>19.270499999999998</v>
+        <v>19.934999999999999</v>
       </c>
       <c r="I97" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J97" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -12023,11 +12030,11 @@
       </c>
       <c r="H98" s="52">
         <f t="shared" si="1"/>
-        <v>19.270499999999998</v>
+        <v>19.934999999999999</v>
       </c>
       <c r="I98" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J98" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -12058,11 +12065,11 @@
       </c>
       <c r="H99" s="51">
         <f t="shared" si="1"/>
-        <v>35.017499999999998</v>
+        <v>36.224999999999994</v>
       </c>
       <c r="I99" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="J99" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -12163,11 +12170,11 @@
       </c>
       <c r="H102" s="52">
         <f t="shared" si="1"/>
-        <v>22.3155</v>
+        <v>23.085000000000001</v>
       </c>
       <c r="I102" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J102" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -12198,15 +12205,15 @@
       </c>
       <c r="H103" s="51">
         <f t="shared" si="1"/>
-        <v>135.81936999999999</v>
+        <v>142.64599999999999</v>
       </c>
       <c r="I103" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.24981245311327827</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J103" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
-        <v>REVIEW</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -12262,7 +12269,10 @@
       <c r="G105" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H105" s="53"/>
+      <c r="H105" s="53" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I105" s="24"/>
       <c r="J105" s="24"/>
     </row>
@@ -12325,11 +12335,11 @@
       </c>
       <c r="H107" s="51">
         <f t="shared" si="1"/>
-        <v>15.935499999999999</v>
+        <v>16.484999999999999</v>
       </c>
       <c r="I107" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J107" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -12360,11 +12370,11 @@
       </c>
       <c r="H108" s="52">
         <f t="shared" si="1"/>
-        <v>28.4055</v>
+        <v>29.384999999999998</v>
       </c>
       <c r="I108" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J108" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -12395,11 +12405,11 @@
       </c>
       <c r="H109" s="51">
         <f t="shared" si="1"/>
-        <v>15.645499999999998</v>
+        <v>16.184999999999999</v>
       </c>
       <c r="I109" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J109" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -12459,11 +12469,11 @@
       </c>
       <c r="H111" s="51">
         <f t="shared" si="1"/>
-        <v>28.4055</v>
+        <v>29.384999999999998</v>
       </c>
       <c r="I111" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J111" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -12488,11 +12498,11 @@
       </c>
       <c r="H112" s="52">
         <f t="shared" si="1"/>
-        <v>24.635499999999997</v>
+        <v>25.484999999999999</v>
       </c>
       <c r="I112" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J112" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -12519,7 +12529,10 @@
       <c r="G113" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H113" s="53"/>
+      <c r="H113" s="53" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I113" s="24"/>
       <c r="J113" s="24"/>
     </row>
@@ -12722,11 +12735,11 @@
       </c>
       <c r="H119" s="51">
         <f t="shared" si="1"/>
-        <v>36.235499999999995</v>
+        <v>37.484999999999999</v>
       </c>
       <c r="I119" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J119" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -12858,7 +12871,10 @@
       <c r="G123" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H123" s="53"/>
+      <c r="H123" s="53" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I123" s="24"/>
       <c r="J123" s="24"/>
     </row>
@@ -12886,11 +12902,11 @@
       </c>
       <c r="H124" s="52">
         <f t="shared" si="1"/>
-        <v>28.985499999999998</v>
+        <v>29.984999999999999</v>
       </c>
       <c r="I124" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J124" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -12921,11 +12937,11 @@
       </c>
       <c r="H125" s="51">
         <f t="shared" si="1"/>
-        <v>21.735499999999998</v>
+        <v>22.484999999999999</v>
       </c>
       <c r="I125" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J125" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -12991,11 +13007,11 @@
       </c>
       <c r="H127" s="51">
         <f t="shared" si="1"/>
-        <v>21.735499999999998</v>
+        <v>22.484999999999999</v>
       </c>
       <c r="I127" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J127" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -13061,11 +13077,11 @@
       </c>
       <c r="H129" s="51">
         <f t="shared" si="1"/>
-        <v>21.735499999999998</v>
+        <v>22.484999999999999</v>
       </c>
       <c r="I129" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J129" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -13095,7 +13111,12 @@
         <v>6.99</v>
       </c>
       <c r="H130" s="52">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H130:H193" si="2">IF(G130&lt;=5,G130*1.6,
+IF(G130&lt;=10,G130*1.55,
+IF(G130&lt;=25,G130*1.5,
+IF(G130&lt;=50,G130*1.4,
+IF(G130&lt;=100,G130*1.4,
+G130*1.4)))))</f>
         <v>10.8345</v>
       </c>
       <c r="I130" s="34">
@@ -13124,7 +13145,7 @@
         <v>2.99</v>
       </c>
       <c r="H131" s="51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.7840000000000007</v>
       </c>
       <c r="I131" s="32">
@@ -13159,7 +13180,7 @@
         <v>25.65</v>
       </c>
       <c r="H132" s="52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>35.909999999999997</v>
       </c>
       <c r="I132" s="34">
@@ -13194,7 +13215,7 @@
         <v>6.59</v>
       </c>
       <c r="H133" s="51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10.214499999999999</v>
       </c>
       <c r="I133" s="32">
@@ -13229,12 +13250,7 @@
         <v>9.99</v>
       </c>
       <c r="H134" s="52">
-        <f t="shared" ref="H134:H197" si="2">IF(G134&lt;=5,G134*1.6,
-IF(G134&lt;=10,G134*1.55,
-IF(G134&lt;=25,G134*1.45,
-IF(G134&lt;=50,G134*1.4,
-IF(G134&lt;=100,G134*1.35,
-G134*1.333)))))</f>
+        <f t="shared" si="2"/>
         <v>15.484500000000001</v>
       </c>
       <c r="I134" s="34">
@@ -13270,11 +13286,11 @@
       </c>
       <c r="H135" s="51">
         <f t="shared" si="2"/>
-        <v>28.985499999999998</v>
+        <v>29.984999999999999</v>
       </c>
       <c r="I135" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J135" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -13340,11 +13356,11 @@
       </c>
       <c r="H137" s="51">
         <f t="shared" si="2"/>
-        <v>21.735499999999998</v>
+        <v>22.484999999999999</v>
       </c>
       <c r="I137" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J137" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -13375,11 +13391,11 @@
       </c>
       <c r="H138" s="52">
         <f t="shared" si="2"/>
-        <v>27.825500000000002</v>
+        <v>28.785000000000004</v>
       </c>
       <c r="I138" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J138" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -13410,11 +13426,11 @@
       </c>
       <c r="H139" s="51">
         <f t="shared" si="2"/>
-        <v>19.270499999999998</v>
+        <v>19.934999999999999</v>
       </c>
       <c r="I139" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J139" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -13445,11 +13461,11 @@
       </c>
       <c r="H140" s="52">
         <f t="shared" si="2"/>
-        <v>18.110499999999998</v>
+        <v>18.734999999999999</v>
       </c>
       <c r="I140" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.3103448275862068</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J140" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -13480,11 +13496,11 @@
       </c>
       <c r="H141" s="51">
         <f t="shared" si="2"/>
-        <v>15.2105</v>
+        <v>15.734999999999999</v>
       </c>
       <c r="I141" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J141" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -13515,11 +13531,11 @@
       </c>
       <c r="H142" s="52">
         <f t="shared" si="2"/>
-        <v>16.950499999999998</v>
+        <v>17.535</v>
       </c>
       <c r="I142" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J142" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -13550,11 +13566,11 @@
       </c>
       <c r="H143" s="51">
         <f t="shared" si="2"/>
-        <v>14.6305</v>
+        <v>15.135</v>
       </c>
       <c r="I143" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J143" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -13585,11 +13601,11 @@
       </c>
       <c r="H144" s="52">
         <f t="shared" si="2"/>
-        <v>16.660499999999999</v>
+        <v>17.234999999999999</v>
       </c>
       <c r="I144" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J144" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -13620,11 +13636,11 @@
       </c>
       <c r="H145" s="51">
         <f t="shared" si="2"/>
-        <v>25.795499999999997</v>
+        <v>26.684999999999999</v>
       </c>
       <c r="I145" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J145" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -13795,11 +13811,11 @@
       </c>
       <c r="H150" s="52">
         <f t="shared" si="2"/>
-        <v>15.7905</v>
+        <v>16.335000000000001</v>
       </c>
       <c r="I150" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J150" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -13830,11 +13846,11 @@
       </c>
       <c r="H151" s="51">
         <f t="shared" si="2"/>
-        <v>34.4955</v>
+        <v>35.685000000000002</v>
       </c>
       <c r="I151" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333343</v>
       </c>
       <c r="J151" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -13900,11 +13916,11 @@
       </c>
       <c r="H153" s="51">
         <f t="shared" si="2"/>
-        <v>23.185500000000001</v>
+        <v>23.984999999999999</v>
       </c>
       <c r="I153" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J153" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -14040,11 +14056,11 @@
       </c>
       <c r="H157" s="51">
         <f t="shared" si="2"/>
-        <v>35.8005</v>
+        <v>37.035000000000004</v>
       </c>
       <c r="I157" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J157" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -14110,11 +14126,11 @@
       </c>
       <c r="H159" s="51">
         <f t="shared" si="2"/>
-        <v>14.775499999999999</v>
+        <v>15.285</v>
       </c>
       <c r="I159" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J159" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -14180,11 +14196,11 @@
       </c>
       <c r="H161" s="51">
         <f t="shared" si="2"/>
-        <v>21.880499999999998</v>
+        <v>22.634999999999998</v>
       </c>
       <c r="I161" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="J161" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -14285,11 +14301,11 @@
       </c>
       <c r="H164" s="52">
         <f t="shared" si="2"/>
-        <v>21.735499999999998</v>
+        <v>22.484999999999999</v>
       </c>
       <c r="I164" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J164" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -14320,11 +14336,11 @@
       </c>
       <c r="H165" s="51">
         <f t="shared" si="2"/>
-        <v>21.735499999999998</v>
+        <v>22.484999999999999</v>
       </c>
       <c r="I165" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J165" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -14666,7 +14682,10 @@
       <c r="G175" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H175" s="53"/>
+      <c r="H175" s="53" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I175" s="24"/>
       <c r="J175" s="24"/>
     </row>
@@ -14694,11 +14713,11 @@
       </c>
       <c r="H176" s="52">
         <f t="shared" si="2"/>
-        <v>29.710499999999996</v>
+        <v>30.734999999999999</v>
       </c>
       <c r="I176" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J176" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -14729,11 +14748,11 @@
       </c>
       <c r="H177" s="51">
         <f t="shared" si="2"/>
-        <v>26.810499999999998</v>
+        <v>27.734999999999999</v>
       </c>
       <c r="I177" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J177" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -14799,11 +14818,11 @@
       </c>
       <c r="H179" s="51">
         <f t="shared" si="2"/>
-        <v>26.810499999999998</v>
+        <v>27.734999999999999</v>
       </c>
       <c r="I179" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J179" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -14834,11 +14853,11 @@
       </c>
       <c r="H180" s="52">
         <f t="shared" si="2"/>
-        <v>28.985499999999998</v>
+        <v>29.984999999999999</v>
       </c>
       <c r="I180" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J180" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -14869,11 +14888,11 @@
       </c>
       <c r="H181" s="51">
         <f t="shared" si="2"/>
-        <v>15.935499999999999</v>
+        <v>16.484999999999999</v>
       </c>
       <c r="I181" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J181" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -14904,11 +14923,11 @@
       </c>
       <c r="H182" s="52">
         <f t="shared" si="2"/>
-        <v>25.650500000000001</v>
+        <v>26.535000000000004</v>
       </c>
       <c r="I182" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J182" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -14939,11 +14958,11 @@
       </c>
       <c r="H183" s="51">
         <f t="shared" si="2"/>
-        <v>28.985499999999998</v>
+        <v>29.984999999999999</v>
       </c>
       <c r="I183" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J183" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -15149,11 +15168,11 @@
       </c>
       <c r="H189" s="51">
         <f t="shared" si="2"/>
-        <v>17.240500000000001</v>
+        <v>17.835000000000001</v>
       </c>
       <c r="I189" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J189" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -15184,11 +15203,11 @@
       </c>
       <c r="H190" s="52">
         <f t="shared" si="2"/>
-        <v>21.1555</v>
+        <v>21.884999999999998</v>
       </c>
       <c r="I190" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="J190" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -15219,11 +15238,11 @@
       </c>
       <c r="H191" s="51">
         <f t="shared" si="2"/>
-        <v>20.575499999999998</v>
+        <v>21.285</v>
       </c>
       <c r="I191" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J191" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -15323,12 +15342,17 @@
         <v>14.79</v>
       </c>
       <c r="H194" s="52">
-        <f t="shared" si="2"/>
-        <v>21.445499999999999</v>
+        <f t="shared" ref="H194:H257" si="3">IF(G194&lt;=5,G194*1.6,
+IF(G194&lt;=10,G194*1.55,
+IF(G194&lt;=25,G194*1.5,
+IF(G194&lt;=50,G194*1.4,
+IF(G194&lt;=100,G194*1.4,
+G194*1.4)))))</f>
+        <v>22.184999999999999</v>
       </c>
       <c r="I194" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J194" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -15358,12 +15382,12 @@
         <v>61.79</v>
       </c>
       <c r="H195" s="51">
-        <f t="shared" si="2"/>
-        <v>83.416499999999999</v>
+        <f t="shared" si="3"/>
+        <v>86.506</v>
       </c>
       <c r="I195" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925924</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J195" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -15393,7 +15417,7 @@
         <v>49.99</v>
       </c>
       <c r="H196" s="52">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>69.986000000000004</v>
       </c>
       <c r="I196" s="34">
@@ -15428,12 +15452,12 @@
         <v>14.79</v>
       </c>
       <c r="H197" s="51">
-        <f t="shared" si="2"/>
-        <v>21.445499999999999</v>
+        <f t="shared" si="3"/>
+        <v>22.184999999999999</v>
       </c>
       <c r="I197" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J197" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -15460,7 +15484,10 @@
       <c r="G198" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H198" s="53"/>
+      <c r="H198" s="53" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I198" s="24"/>
       <c r="J198" s="24"/>
     </row>
@@ -15487,17 +15514,12 @@
         <v>11.79</v>
       </c>
       <c r="H199" s="51">
-        <f t="shared" ref="H199:H261" si="3">IF(G199&lt;=5,G199*1.6,
-IF(G199&lt;=10,G199*1.55,
-IF(G199&lt;=25,G199*1.45,
-IF(G199&lt;=50,G199*1.4,
-IF(G199&lt;=100,G199*1.35,
-G199*1.333)))))</f>
-        <v>17.095499999999998</v>
+        <f t="shared" si="3"/>
+        <v>17.684999999999999</v>
       </c>
       <c r="I199" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J199" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -15734,7 +15756,10 @@
       <c r="G206" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H206" s="53"/>
+      <c r="H206" s="53" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I206" s="24"/>
       <c r="J206" s="24"/>
     </row>
@@ -15762,11 +15787,11 @@
       </c>
       <c r="H207" s="51">
         <f t="shared" si="3"/>
-        <v>34.350500000000004</v>
+        <v>35.535000000000004</v>
       </c>
       <c r="I207" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620696</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J207" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -15797,11 +15822,11 @@
       </c>
       <c r="H208" s="52">
         <f t="shared" si="3"/>
-        <v>27.1005</v>
+        <v>28.035000000000004</v>
       </c>
       <c r="I208" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J208" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -15832,11 +15857,11 @@
       </c>
       <c r="H209" s="51">
         <f t="shared" si="3"/>
-        <v>27.1005</v>
+        <v>28.035000000000004</v>
       </c>
       <c r="I209" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J209" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -15902,11 +15927,11 @@
       </c>
       <c r="H211" s="51">
         <f t="shared" si="3"/>
-        <v>34.350500000000004</v>
+        <v>35.535000000000004</v>
       </c>
       <c r="I211" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620696</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J211" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -15972,11 +15997,11 @@
       </c>
       <c r="H213" s="51">
         <f t="shared" si="3"/>
-        <v>36.235499999999995</v>
+        <v>37.484999999999999</v>
       </c>
       <c r="I213" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J213" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -16007,11 +16032,11 @@
       </c>
       <c r="H214" s="52">
         <f t="shared" si="3"/>
-        <v>31.885499999999997</v>
+        <v>32.984999999999999</v>
       </c>
       <c r="I214" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J214" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -16042,11 +16067,11 @@
       </c>
       <c r="H215" s="51">
         <f t="shared" si="3"/>
-        <v>26.810499999999998</v>
+        <v>27.734999999999999</v>
       </c>
       <c r="I215" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J215" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -16077,11 +16102,11 @@
       </c>
       <c r="H216" s="52">
         <f t="shared" si="3"/>
-        <v>18.110499999999998</v>
+        <v>18.734999999999999</v>
       </c>
       <c r="I216" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.3103448275862068</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J216" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -16143,7 +16168,10 @@
       <c r="G218" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H218" s="53"/>
+      <c r="H218" s="53" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I218" s="24"/>
       <c r="J218" s="24"/>
     </row>
@@ -16241,11 +16269,11 @@
       </c>
       <c r="H221" s="51">
         <f t="shared" si="3"/>
-        <v>18.8355</v>
+        <v>19.484999999999999</v>
       </c>
       <c r="I221" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J221" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -16276,11 +16304,11 @@
       </c>
       <c r="H222" s="52">
         <f t="shared" si="3"/>
-        <v>26.085499999999996</v>
+        <v>26.984999999999999</v>
       </c>
       <c r="I222" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J222" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -16311,11 +16339,11 @@
       </c>
       <c r="H223" s="51">
         <f t="shared" si="3"/>
-        <v>20.285499999999999</v>
+        <v>20.984999999999999</v>
       </c>
       <c r="I223" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J223" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -16589,11 +16617,11 @@
       </c>
       <c r="H231" s="51">
         <f t="shared" si="3"/>
-        <v>28.985499999999998</v>
+        <v>29.984999999999999</v>
       </c>
       <c r="I231" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J231" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -16740,7 +16768,10 @@
       <c r="G236" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H236" s="53"/>
+      <c r="H236" s="53" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I236" s="24"/>
       <c r="J236" s="24"/>
     </row>
@@ -16768,11 +16799,11 @@
       </c>
       <c r="H237" s="51">
         <f t="shared" si="3"/>
-        <v>14.920499999999999</v>
+        <v>15.434999999999999</v>
       </c>
       <c r="I237" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J237" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -16803,11 +16834,11 @@
       </c>
       <c r="H238" s="52">
         <f t="shared" si="3"/>
-        <v>20.285499999999999</v>
+        <v>20.984999999999999</v>
       </c>
       <c r="I238" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J238" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -16838,11 +16869,11 @@
       </c>
       <c r="H239" s="51">
         <f t="shared" si="3"/>
-        <v>20.285499999999999</v>
+        <v>20.984999999999999</v>
       </c>
       <c r="I239" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J239" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -16873,11 +16904,11 @@
       </c>
       <c r="H240" s="52">
         <f t="shared" si="3"/>
-        <v>14.920499999999999</v>
+        <v>15.434999999999999</v>
       </c>
       <c r="I240" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J240" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -16908,11 +16939,11 @@
       </c>
       <c r="H241" s="51">
         <f t="shared" si="3"/>
-        <v>34.785499999999999</v>
+        <v>35.984999999999999</v>
       </c>
       <c r="I241" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J241" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -17114,7 +17145,10 @@
       <c r="G247" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H247" s="53"/>
+      <c r="H247" s="53" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I247" s="24"/>
       <c r="J247" s="24"/>
     </row>
@@ -17171,11 +17205,11 @@
       </c>
       <c r="H249" s="51">
         <f t="shared" si="3"/>
-        <v>25.650500000000001</v>
+        <v>26.535000000000004</v>
       </c>
       <c r="I249" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J249" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -17270,11 +17304,11 @@
       </c>
       <c r="H252" s="52">
         <f t="shared" si="3"/>
-        <v>19.415500000000002</v>
+        <v>20.085000000000001</v>
       </c>
       <c r="I252" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J252" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -17305,11 +17339,11 @@
       </c>
       <c r="H253" s="51">
         <f t="shared" si="3"/>
-        <v>30.435499999999998</v>
+        <v>31.484999999999999</v>
       </c>
       <c r="I253" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J253" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -17375,11 +17409,11 @@
       </c>
       <c r="H255" s="51">
         <f t="shared" si="3"/>
-        <v>31.885499999999997</v>
+        <v>32.984999999999999</v>
       </c>
       <c r="I255" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J255" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -17410,11 +17444,11 @@
       </c>
       <c r="H256" s="52">
         <f t="shared" si="3"/>
-        <v>34.060499999999998</v>
+        <v>35.234999999999999</v>
       </c>
       <c r="I256" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J256" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -17445,11 +17479,11 @@
       </c>
       <c r="H257" s="51">
         <f t="shared" si="3"/>
-        <v>33.335499999999996</v>
+        <v>34.484999999999999</v>
       </c>
       <c r="I257" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J257" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -17479,7 +17513,12 @@
         <v>25.49</v>
       </c>
       <c r="H258" s="52">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="H258:H321" si="4">IF(G258&lt;=5,G258*1.6,
+IF(G258&lt;=10,G258*1.55,
+IF(G258&lt;=25,G258*1.5,
+IF(G258&lt;=50,G258*1.4,
+IF(G258&lt;=100,G258*1.4,
+G258*1.4)))))</f>
         <v>35.685999999999993</v>
       </c>
       <c r="I258" s="34">
@@ -17514,7 +17553,7 @@
         <v>9.49</v>
       </c>
       <c r="H259" s="51">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>14.7095</v>
       </c>
       <c r="I259" s="32">
@@ -17546,7 +17585,10 @@
       <c r="G260" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H260" s="53"/>
+      <c r="H260" s="53" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I260" s="24"/>
       <c r="J260" s="24"/>
     </row>
@@ -17573,12 +17615,12 @@
         <v>16.989999999999998</v>
       </c>
       <c r="H261" s="51">
-        <f t="shared" si="3"/>
-        <v>24.635499999999997</v>
+        <f t="shared" si="4"/>
+        <v>25.484999999999999</v>
       </c>
       <c r="I261" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J261" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -17608,17 +17650,12 @@
         <v>19.350000000000001</v>
       </c>
       <c r="H262" s="52">
-        <f t="shared" ref="H262:H325" si="4">IF(G262&lt;=5,G262*1.6,
-IF(G262&lt;=10,G262*1.55,
-IF(G262&lt;=25,G262*1.45,
-IF(G262&lt;=50,G262*1.4,
-IF(G262&lt;=100,G262*1.35,
-G262*1.333)))))</f>
-        <v>28.057500000000001</v>
+        <f t="shared" si="4"/>
+        <v>29.025000000000002</v>
       </c>
       <c r="I262" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J262" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -17649,11 +17686,11 @@
       </c>
       <c r="H263" s="51">
         <f t="shared" si="4"/>
-        <v>23.997499999999999</v>
+        <v>24.825000000000003</v>
       </c>
       <c r="I263" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J263" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -17684,11 +17721,11 @@
       </c>
       <c r="H264" s="52">
         <f t="shared" si="4"/>
-        <v>20.140499999999999</v>
+        <v>20.835000000000001</v>
       </c>
       <c r="I264" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J264" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -17719,11 +17756,11 @@
       </c>
       <c r="H265" s="51">
         <f t="shared" si="4"/>
-        <v>32.030499999999996</v>
+        <v>33.134999999999998</v>
       </c>
       <c r="I265" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J265" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -17789,11 +17826,11 @@
       </c>
       <c r="H267" s="51">
         <f t="shared" si="4"/>
-        <v>22.750499999999999</v>
+        <v>23.535</v>
       </c>
       <c r="I267" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J267" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -17824,11 +17861,11 @@
       </c>
       <c r="H268" s="52">
         <f t="shared" si="4"/>
-        <v>24.055499999999999</v>
+        <v>24.884999999999998</v>
       </c>
       <c r="I268" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="J268" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -17925,7 +17962,10 @@
       <c r="G271" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H271" s="53"/>
+      <c r="H271" s="53" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I271" s="24"/>
       <c r="J271" s="24"/>
     </row>
@@ -18023,11 +18063,11 @@
       </c>
       <c r="H274" s="52">
         <f t="shared" si="4"/>
-        <v>34.930500000000002</v>
+        <v>36.134999999999998</v>
       </c>
       <c r="I274" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620696</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J274" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -18128,11 +18168,11 @@
       </c>
       <c r="H277" s="51">
         <f t="shared" si="4"/>
-        <v>19.560500000000001</v>
+        <v>20.234999999999999</v>
       </c>
       <c r="I277" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J277" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -18163,11 +18203,11 @@
       </c>
       <c r="H278" s="52">
         <f t="shared" si="4"/>
-        <v>23.910499999999995</v>
+        <v>24.734999999999999</v>
       </c>
       <c r="I278" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J278" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -18233,11 +18273,11 @@
       </c>
       <c r="H280" s="52">
         <f t="shared" si="4"/>
-        <v>35.510499999999993</v>
+        <v>36.734999999999999</v>
       </c>
       <c r="I280" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.3103448275862068</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J280" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -18264,7 +18304,10 @@
       <c r="G281" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H281" s="53"/>
+      <c r="H281" s="53" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I281" s="24"/>
       <c r="J281" s="24"/>
     </row>
@@ -18327,11 +18370,11 @@
       </c>
       <c r="H283" s="51">
         <f t="shared" si="4"/>
-        <v>27.245499999999996</v>
+        <v>28.184999999999999</v>
       </c>
       <c r="I283" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J283" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -18362,11 +18405,11 @@
       </c>
       <c r="H284" s="52">
         <f t="shared" si="4"/>
-        <v>28.260499999999997</v>
+        <v>29.234999999999999</v>
       </c>
       <c r="I284" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J284" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -18498,7 +18541,10 @@
       <c r="G288" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H288" s="53"/>
+      <c r="H288" s="53" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I288" s="24"/>
       <c r="J288" s="24"/>
     </row>
@@ -18549,11 +18595,11 @@
       </c>
       <c r="H290" s="51">
         <f t="shared" si="4"/>
-        <v>19.560500000000001</v>
+        <v>20.234999999999999</v>
       </c>
       <c r="I290" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J290" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -18607,11 +18653,11 @@
       </c>
       <c r="H292" s="51">
         <f t="shared" si="4"/>
-        <v>25.360499999999998</v>
+        <v>26.234999999999999</v>
       </c>
       <c r="I292" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J292" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -18665,11 +18711,11 @@
       </c>
       <c r="H294" s="51">
         <f t="shared" si="4"/>
-        <v>20.285499999999999</v>
+        <v>20.984999999999999</v>
       </c>
       <c r="I294" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J294" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -18723,11 +18769,11 @@
       </c>
       <c r="H296" s="51">
         <f t="shared" si="4"/>
-        <v>27.535499999999995</v>
+        <v>28.484999999999999</v>
       </c>
       <c r="I296" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J296" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -18781,11 +18827,11 @@
       </c>
       <c r="H298" s="51">
         <f t="shared" si="4"/>
-        <v>23.185500000000001</v>
+        <v>23.984999999999999</v>
       </c>
       <c r="I298" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J298" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -18839,11 +18885,11 @@
       </c>
       <c r="H300" s="51">
         <f t="shared" si="4"/>
-        <v>23.185500000000001</v>
+        <v>23.984999999999999</v>
       </c>
       <c r="I300" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J300" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -18897,11 +18943,11 @@
       </c>
       <c r="H302" s="51">
         <f t="shared" si="4"/>
-        <v>21.735499999999998</v>
+        <v>22.484999999999999</v>
       </c>
       <c r="I302" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J302" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -18955,11 +19001,11 @@
       </c>
       <c r="H304" s="51">
         <f t="shared" si="4"/>
-        <v>26.810499999999998</v>
+        <v>27.734999999999999</v>
       </c>
       <c r="I304" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J304" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19013,11 +19059,11 @@
       </c>
       <c r="H306" s="51">
         <f t="shared" si="4"/>
-        <v>15.2105</v>
+        <v>15.734999999999999</v>
       </c>
       <c r="I306" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J306" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19100,11 +19146,11 @@
       </c>
       <c r="H309" s="52">
         <f t="shared" si="4"/>
-        <v>20.285499999999999</v>
+        <v>20.984999999999999</v>
       </c>
       <c r="I309" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J309" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19129,11 +19175,11 @@
       </c>
       <c r="H310" s="51">
         <f t="shared" si="4"/>
-        <v>101.9115</v>
+        <v>105.68599999999999</v>
       </c>
       <c r="I310" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925936</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J310" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19158,11 +19204,11 @@
       </c>
       <c r="H311" s="52">
         <f t="shared" si="4"/>
-        <v>20.285499999999999</v>
+        <v>20.984999999999999</v>
       </c>
       <c r="I311" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J311" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19187,11 +19233,11 @@
       </c>
       <c r="H312" s="51">
         <f t="shared" si="4"/>
-        <v>101.9115</v>
+        <v>105.68599999999999</v>
       </c>
       <c r="I312" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925936</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J312" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19216,11 +19262,11 @@
       </c>
       <c r="H313" s="52">
         <f t="shared" si="4"/>
-        <v>20.285499999999999</v>
+        <v>20.984999999999999</v>
       </c>
       <c r="I313" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J313" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19245,11 +19291,11 @@
       </c>
       <c r="H314" s="51">
         <f t="shared" si="4"/>
-        <v>101.9115</v>
+        <v>105.68599999999999</v>
       </c>
       <c r="I314" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925936</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J314" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19274,11 +19320,11 @@
       </c>
       <c r="H315" s="52">
         <f t="shared" si="4"/>
-        <v>20.285499999999999</v>
+        <v>20.984999999999999</v>
       </c>
       <c r="I315" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J315" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19303,11 +19349,11 @@
       </c>
       <c r="H316" s="51">
         <f t="shared" si="4"/>
-        <v>101.9115</v>
+        <v>105.68599999999999</v>
       </c>
       <c r="I316" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925936</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J316" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19332,11 +19378,11 @@
       </c>
       <c r="H317" s="52">
         <f t="shared" si="4"/>
-        <v>18.6905</v>
+        <v>19.335000000000001</v>
       </c>
       <c r="I317" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J317" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19361,11 +19407,11 @@
       </c>
       <c r="H318" s="51">
         <f t="shared" si="4"/>
-        <v>103.9365</v>
+        <v>107.78599999999999</v>
       </c>
       <c r="I318" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.2592592592592593</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J318" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19390,11 +19436,11 @@
       </c>
       <c r="H319" s="52">
         <f t="shared" si="4"/>
-        <v>20.285499999999999</v>
+        <v>20.984999999999999</v>
       </c>
       <c r="I319" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J319" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19419,11 +19465,11 @@
       </c>
       <c r="H320" s="51">
         <f t="shared" si="4"/>
-        <v>101.9115</v>
+        <v>105.68599999999999</v>
       </c>
       <c r="I320" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925936</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J320" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19448,11 +19494,11 @@
       </c>
       <c r="H321" s="52">
         <f t="shared" si="4"/>
-        <v>28.985499999999998</v>
+        <v>29.984999999999999</v>
       </c>
       <c r="I321" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J321" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19476,16 +19522,21 @@
         <v>119.89</v>
       </c>
       <c r="H322" s="51">
-        <f t="shared" si="4"/>
-        <v>159.81336999999999</v>
+        <f t="shared" ref="H322:H385" si="5">IF(G322&lt;=5,G322*1.6,
+IF(G322&lt;=10,G322*1.55,
+IF(G322&lt;=25,G322*1.5,
+IF(G322&lt;=50,G322*1.4,
+IF(G322&lt;=100,G322*1.4,
+G322*1.4)))))</f>
+        <v>167.846</v>
       </c>
       <c r="I322" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.24981245311327827</v>
+        <v>0.28571428571428575</v>
       </c>
       <c r="J322" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
-        <v>REVIEW</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="323" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -19505,12 +19556,12 @@
         <v>17.989999999999998</v>
       </c>
       <c r="H323" s="52">
-        <f t="shared" si="4"/>
-        <v>26.085499999999996</v>
+        <f t="shared" si="5"/>
+        <v>26.984999999999999</v>
       </c>
       <c r="I323" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J323" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19534,16 +19585,16 @@
         <v>107.29</v>
       </c>
       <c r="H324" s="51">
-        <f t="shared" si="4"/>
-        <v>143.01757000000001</v>
+        <f t="shared" si="5"/>
+        <v>150.20599999999999</v>
       </c>
       <c r="I324" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.24981245311327832</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J324" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
-        <v>REVIEW</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="325" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -19563,7 +19614,7 @@
         <v>6.69</v>
       </c>
       <c r="H325" s="52">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.3695</v>
       </c>
       <c r="I325" s="32">
@@ -19592,12 +19643,7 @@
         <v>39.99</v>
       </c>
       <c r="H326" s="51">
-        <f t="shared" ref="H326:H389" si="5">IF(G326&lt;=5,G326*1.6,
-IF(G326&lt;=10,G326*1.55,
-IF(G326&lt;=25,G326*1.45,
-IF(G326&lt;=50,G326*1.4,
-IF(G326&lt;=100,G326*1.35,
-G326*1.333)))))</f>
+        <f t="shared" si="5"/>
         <v>55.985999999999997</v>
       </c>
       <c r="I326" s="34">
@@ -19627,11 +19673,11 @@
       </c>
       <c r="H327" s="52">
         <f t="shared" si="5"/>
-        <v>21.0105</v>
+        <v>21.734999999999999</v>
       </c>
       <c r="I327" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J327" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19656,11 +19702,11 @@
       </c>
       <c r="H328" s="51">
         <f t="shared" si="5"/>
-        <v>114.73650000000001</v>
+        <v>118.98599999999999</v>
       </c>
       <c r="I328" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925936</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J328" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19685,11 +19731,11 @@
       </c>
       <c r="H329" s="52">
         <f t="shared" si="5"/>
-        <v>22.4605</v>
+        <v>23.234999999999999</v>
       </c>
       <c r="I329" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J329" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19772,11 +19818,11 @@
       </c>
       <c r="H332" s="51">
         <f t="shared" si="5"/>
-        <v>28.840499999999999</v>
+        <v>29.835000000000001</v>
       </c>
       <c r="I332" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J332" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19859,11 +19905,11 @@
       </c>
       <c r="H335" s="52">
         <f t="shared" si="5"/>
-        <v>28.260499999999997</v>
+        <v>29.234999999999999</v>
       </c>
       <c r="I335" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J335" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19946,11 +19992,11 @@
       </c>
       <c r="H338" s="51">
         <f t="shared" si="5"/>
-        <v>34.785499999999999</v>
+        <v>35.984999999999999</v>
       </c>
       <c r="I338" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J338" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -19975,11 +20021,11 @@
       </c>
       <c r="H339" s="52">
         <f t="shared" si="5"/>
-        <v>21.0105</v>
+        <v>21.734999999999999</v>
       </c>
       <c r="I339" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J339" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -20033,11 +20079,11 @@
       </c>
       <c r="H341" s="52">
         <f t="shared" si="5"/>
-        <v>72.211500000000001</v>
+        <v>74.885999999999996</v>
       </c>
       <c r="I341" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925924</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J341" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -20207,11 +20253,11 @@
       </c>
       <c r="H347" s="52">
         <f t="shared" si="5"/>
-        <v>28.260499999999997</v>
+        <v>29.234999999999999</v>
       </c>
       <c r="I347" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J347" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -20410,11 +20456,11 @@
       </c>
       <c r="H354" s="51">
         <f t="shared" si="5"/>
-        <v>15.935499999999999</v>
+        <v>16.484999999999999</v>
       </c>
       <c r="I354" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J354" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -20439,11 +20485,11 @@
       </c>
       <c r="H355" s="52">
         <f t="shared" si="5"/>
-        <v>78.286500000000004</v>
+        <v>81.185999999999993</v>
       </c>
       <c r="I355" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925924</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J355" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -20555,11 +20601,11 @@
       </c>
       <c r="H359" s="52">
         <f t="shared" si="5"/>
-        <v>28.260499999999997</v>
+        <v>29.234999999999999</v>
       </c>
       <c r="I359" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J359" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -20787,11 +20833,11 @@
       </c>
       <c r="H367" s="52">
         <f t="shared" si="5"/>
-        <v>28.985499999999998</v>
+        <v>29.984999999999999</v>
       </c>
       <c r="I367" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J367" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -21077,11 +21123,11 @@
       </c>
       <c r="H377" s="52">
         <f t="shared" si="5"/>
-        <v>20.720499999999998</v>
+        <v>21.434999999999999</v>
       </c>
       <c r="I377" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J377" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -21106,11 +21152,11 @@
       </c>
       <c r="H378" s="51">
         <f t="shared" si="5"/>
-        <v>28.985499999999998</v>
+        <v>29.984999999999999</v>
       </c>
       <c r="I378" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J378" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -21135,15 +21181,15 @@
       </c>
       <c r="H379" s="52">
         <f t="shared" si="5"/>
-        <v>143.81736999999998</v>
+        <v>151.04599999999999</v>
       </c>
       <c r="I379" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.24981245311327824</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J379" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
-        <v>REVIEW</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="380" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -21309,11 +21355,11 @@
       </c>
       <c r="H385" s="52">
         <f t="shared" si="5"/>
-        <v>35.510499999999993</v>
+        <v>36.734999999999999</v>
       </c>
       <c r="I385" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.3103448275862068</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J385" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -21337,12 +21383,17 @@
         <v>11.99</v>
       </c>
       <c r="H386" s="51">
-        <f t="shared" si="5"/>
-        <v>17.3855</v>
+        <f t="shared" ref="H386:H449" si="6">IF(G386&lt;=5,G386*1.6,
+IF(G386&lt;=10,G386*1.55,
+IF(G386&lt;=25,G386*1.5,
+IF(G386&lt;=50,G386*1.4,
+IF(G386&lt;=100,G386*1.4,
+G386*1.4)))))</f>
+        <v>17.984999999999999</v>
       </c>
       <c r="I386" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J386" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -21366,12 +21417,12 @@
         <v>71.489999999999995</v>
       </c>
       <c r="H387" s="52">
-        <f t="shared" si="5"/>
-        <v>96.511499999999998</v>
+        <f t="shared" si="6"/>
+        <v>100.08599999999998</v>
       </c>
       <c r="I387" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.2592592592592593</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J387" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -21395,12 +21446,12 @@
         <v>10.99</v>
       </c>
       <c r="H388" s="51">
-        <f t="shared" si="5"/>
-        <v>15.935499999999999</v>
+        <f t="shared" si="6"/>
+        <v>16.484999999999999</v>
       </c>
       <c r="I388" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J388" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -21424,12 +21475,12 @@
         <v>64.989999999999995</v>
       </c>
       <c r="H389" s="52">
-        <f t="shared" si="5"/>
-        <v>87.736499999999992</v>
+        <f t="shared" si="6"/>
+        <v>90.98599999999999</v>
       </c>
       <c r="I389" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925924</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J389" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -21453,12 +21504,7 @@
         <v>1.49</v>
       </c>
       <c r="H390" s="51">
-        <f t="shared" ref="H390:H453" si="6">IF(G390&lt;=5,G390*1.6,
-IF(G390&lt;=10,G390*1.55,
-IF(G390&lt;=25,G390*1.45,
-IF(G390&lt;=50,G390*1.4,
-IF(G390&lt;=100,G390*1.35,
-G390*1.333)))))</f>
+        <f t="shared" si="6"/>
         <v>2.3839999999999999</v>
       </c>
       <c r="I390" s="34">
@@ -21604,11 +21650,11 @@
       </c>
       <c r="H395" s="52">
         <f t="shared" si="6"/>
-        <v>23.910499999999995</v>
+        <v>24.734999999999999</v>
       </c>
       <c r="I395" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J395" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -21662,11 +21708,11 @@
       </c>
       <c r="H397" s="52">
         <f t="shared" si="6"/>
-        <v>26.810499999999998</v>
+        <v>27.734999999999999</v>
       </c>
       <c r="I397" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J397" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -21691,11 +21737,11 @@
       </c>
       <c r="H398" s="51">
         <f t="shared" si="6"/>
-        <v>17.3855</v>
+        <v>17.984999999999999</v>
       </c>
       <c r="I398" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J398" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -21720,11 +21766,11 @@
       </c>
       <c r="H399" s="52">
         <f t="shared" si="6"/>
-        <v>74.236500000000007</v>
+        <v>76.986000000000004</v>
       </c>
       <c r="I399" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.2592592592592593</v>
+        <v>0.28571428571428575</v>
       </c>
       <c r="J399" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -21807,11 +21853,11 @@
       </c>
       <c r="H402" s="51">
         <f t="shared" si="6"/>
-        <v>21.735499999999998</v>
+        <v>22.484999999999999</v>
       </c>
       <c r="I402" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J402" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -21836,11 +21882,11 @@
       </c>
       <c r="H403" s="52">
         <f t="shared" si="6"/>
-        <v>118.11150000000001</v>
+        <v>122.48599999999999</v>
       </c>
       <c r="I403" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925936</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J403" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -22010,11 +22056,11 @@
       </c>
       <c r="H409" s="52">
         <f t="shared" si="6"/>
-        <v>33.335499999999996</v>
+        <v>34.484999999999999</v>
       </c>
       <c r="I409" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J409" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -22242,11 +22288,11 @@
       </c>
       <c r="H417" s="52">
         <f t="shared" si="6"/>
-        <v>32.610499999999995</v>
+        <v>33.734999999999999</v>
       </c>
       <c r="I417" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J417" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -22271,11 +22317,11 @@
       </c>
       <c r="H418" s="51">
         <f t="shared" si="6"/>
-        <v>17.3855</v>
+        <v>17.984999999999999</v>
       </c>
       <c r="I418" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J418" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -22300,11 +22346,11 @@
       </c>
       <c r="H419" s="52">
         <f t="shared" si="6"/>
-        <v>86.386500000000012</v>
+        <v>89.585999999999999</v>
       </c>
       <c r="I419" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925936</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J419" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -22358,11 +22404,11 @@
       </c>
       <c r="H421" s="52">
         <f t="shared" si="6"/>
-        <v>72.751500000000007</v>
+        <v>75.445999999999998</v>
       </c>
       <c r="I421" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.2592592592592593</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J421" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -22387,11 +22433,11 @@
       </c>
       <c r="H422" s="51">
         <f t="shared" si="6"/>
-        <v>17.3855</v>
+        <v>17.984999999999999</v>
       </c>
       <c r="I422" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J422" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -22416,11 +22462,11 @@
       </c>
       <c r="H423" s="52">
         <f t="shared" si="6"/>
-        <v>96.511499999999998</v>
+        <v>100.08599999999998</v>
       </c>
       <c r="I423" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.2592592592592593</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J423" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -22445,11 +22491,11 @@
       </c>
       <c r="H424" s="51">
         <f t="shared" si="6"/>
-        <v>21.735499999999998</v>
+        <v>22.484999999999999</v>
       </c>
       <c r="I424" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J424" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -22474,11 +22520,11 @@
       </c>
       <c r="H425" s="52">
         <f t="shared" si="6"/>
-        <v>118.11150000000001</v>
+        <v>122.48599999999999</v>
       </c>
       <c r="I425" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925936</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J425" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -22532,11 +22578,11 @@
       </c>
       <c r="H427" s="52">
         <f t="shared" si="6"/>
-        <v>80.851500000000001</v>
+        <v>83.845999999999989</v>
       </c>
       <c r="I427" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925924</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J427" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -22590,11 +22636,11 @@
       </c>
       <c r="H429" s="52">
         <f t="shared" si="6"/>
-        <v>76.801500000000004</v>
+        <v>79.646000000000001</v>
       </c>
       <c r="I429" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.2592592592592593</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J429" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -22619,11 +22665,11 @@
       </c>
       <c r="H430" s="51">
         <f t="shared" si="6"/>
-        <v>19.560500000000001</v>
+        <v>20.234999999999999</v>
       </c>
       <c r="I430" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J430" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -22648,11 +22694,11 @@
       </c>
       <c r="H431" s="52">
         <f t="shared" si="6"/>
-        <v>106.6365</v>
+        <v>110.58599999999998</v>
       </c>
       <c r="I431" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.2592592592592593</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J431" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -22677,11 +22723,11 @@
       </c>
       <c r="H432" s="51">
         <f t="shared" si="6"/>
-        <v>18.8355</v>
+        <v>19.484999999999999</v>
       </c>
       <c r="I432" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J432" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -22824,7 +22870,10 @@
       <c r="G437" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H437" s="53"/>
+      <c r="H437" s="53" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I437" s="24"/>
       <c r="J437" s="24"/>
     </row>
@@ -22922,11 +22971,11 @@
       </c>
       <c r="H440" s="51">
         <f t="shared" si="6"/>
-        <v>21.880499999999998</v>
+        <v>22.634999999999998</v>
       </c>
       <c r="I440" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="J440" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -22957,11 +23006,11 @@
       </c>
       <c r="H441" s="52">
         <f t="shared" si="6"/>
-        <v>16.660499999999999</v>
+        <v>17.234999999999999</v>
       </c>
       <c r="I441" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J441" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -23027,11 +23076,11 @@
       </c>
       <c r="H443" s="52">
         <f t="shared" si="6"/>
-        <v>16.747500000000002</v>
+        <v>17.325000000000003</v>
       </c>
       <c r="I443" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620696</v>
+        <v>0.33333333333333343</v>
       </c>
       <c r="J443" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -23217,11 +23266,11 @@
       </c>
       <c r="H449" s="52">
         <f t="shared" si="6"/>
-        <v>17.3855</v>
+        <v>17.984999999999999</v>
       </c>
       <c r="I449" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J449" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -23247,7 +23296,12 @@
         <v>8.99</v>
       </c>
       <c r="H450" s="51">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="H450:H513" si="7">IF(G450&lt;=5,G450*1.6,
+IF(G450&lt;=10,G450*1.55,
+IF(G450&lt;=25,G450*1.5,
+IF(G450&lt;=50,G450*1.4,
+IF(G450&lt;=100,G450*1.4,
+G450*1.4)))))</f>
         <v>13.9345</v>
       </c>
       <c r="I450" s="34">
@@ -23278,7 +23332,7 @@
         <v>2.99</v>
       </c>
       <c r="H451" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.7840000000000007</v>
       </c>
       <c r="I451" s="32">
@@ -23309,7 +23363,7 @@
         <v>8.99</v>
       </c>
       <c r="H452" s="51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.9345</v>
       </c>
       <c r="I452" s="34">
@@ -23340,7 +23394,7 @@
         <v>6.49</v>
       </c>
       <c r="H453" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10.0595</v>
       </c>
       <c r="I453" s="32">
@@ -23371,12 +23425,7 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="H454" s="51">
-        <f t="shared" ref="H454:H517" si="7">IF(G454&lt;=5,G454*1.6,
-IF(G454&lt;=10,G454*1.55,
-IF(G454&lt;=25,G454*1.45,
-IF(G454&lt;=50,G454*1.4,
-IF(G454&lt;=100,G454*1.35,
-G454*1.333)))))</f>
+        <f t="shared" si="7"/>
         <v>3.9840000000000004</v>
       </c>
       <c r="I454" s="34">
@@ -23685,7 +23734,10 @@
       <c r="G464" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H464" s="53"/>
+      <c r="H464" s="53" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I464" s="24"/>
       <c r="J464" s="24"/>
     </row>
@@ -23713,11 +23765,11 @@
       </c>
       <c r="H465" s="52">
         <f t="shared" si="7"/>
-        <v>28.274999999999999</v>
+        <v>29.25</v>
       </c>
       <c r="I465" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J465" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -23853,11 +23905,11 @@
       </c>
       <c r="H469" s="52">
         <f t="shared" si="7"/>
-        <v>28.622999999999998</v>
+        <v>29.61</v>
       </c>
       <c r="I469" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J469" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -23958,11 +24010,11 @@
       </c>
       <c r="H472" s="51">
         <f t="shared" si="7"/>
-        <v>25.360499999999998</v>
+        <v>26.234999999999999</v>
       </c>
       <c r="I472" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J472" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -23993,11 +24045,11 @@
       </c>
       <c r="H473" s="52">
         <f t="shared" si="7"/>
-        <v>17.3855</v>
+        <v>17.984999999999999</v>
       </c>
       <c r="I473" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J473" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24028,11 +24080,11 @@
       </c>
       <c r="H474" s="51">
         <f t="shared" si="7"/>
-        <v>16.2255</v>
+        <v>16.785</v>
       </c>
       <c r="I474" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620696</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J474" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24061,11 +24113,11 @@
       </c>
       <c r="H475" s="52">
         <f t="shared" si="7"/>
-        <v>16.2255</v>
+        <v>16.785</v>
       </c>
       <c r="I475" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620696</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J475" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24166,11 +24218,11 @@
       </c>
       <c r="H478" s="51">
         <f t="shared" si="7"/>
-        <v>15.152499999999998</v>
+        <v>15.674999999999999</v>
       </c>
       <c r="I478" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J478" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24236,11 +24288,11 @@
       </c>
       <c r="H480" s="51">
         <f t="shared" si="7"/>
-        <v>21.532499999999999</v>
+        <v>22.274999999999999</v>
       </c>
       <c r="I480" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J480" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24358,11 +24410,11 @@
       </c>
       <c r="H484" s="51">
         <f t="shared" si="7"/>
-        <v>19.8505</v>
+        <v>20.535</v>
       </c>
       <c r="I484" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J484" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24387,11 +24439,11 @@
       </c>
       <c r="H485" s="52">
         <f t="shared" si="7"/>
-        <v>19.9955</v>
+        <v>20.684999999999999</v>
       </c>
       <c r="I485" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J485" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24416,11 +24468,11 @@
       </c>
       <c r="H486" s="51">
         <f t="shared" si="7"/>
-        <v>19.8505</v>
+        <v>20.535</v>
       </c>
       <c r="I486" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J486" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24445,11 +24497,11 @@
       </c>
       <c r="H487" s="52">
         <f t="shared" si="7"/>
-        <v>21.387499999999999</v>
+        <v>22.125</v>
       </c>
       <c r="I487" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J487" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24474,11 +24526,11 @@
       </c>
       <c r="H488" s="51">
         <f t="shared" si="7"/>
-        <v>16.965</v>
+        <v>17.549999999999997</v>
       </c>
       <c r="I488" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="J488" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24503,11 +24555,11 @@
       </c>
       <c r="H489" s="52">
         <f t="shared" si="7"/>
-        <v>15.2105</v>
+        <v>15.734999999999999</v>
       </c>
       <c r="I489" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J489" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24561,11 +24613,11 @@
       </c>
       <c r="H491" s="52">
         <f t="shared" si="7"/>
-        <v>15.007499999999999</v>
+        <v>15.524999999999999</v>
       </c>
       <c r="I491" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J491" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24590,11 +24642,11 @@
       </c>
       <c r="H492" s="51">
         <f t="shared" si="7"/>
-        <v>15.152499999999998</v>
+        <v>15.674999999999999</v>
       </c>
       <c r="I492" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J492" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24648,11 +24700,11 @@
       </c>
       <c r="H494" s="51">
         <f t="shared" si="7"/>
-        <v>15.2105</v>
+        <v>15.734999999999999</v>
       </c>
       <c r="I494" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J494" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24706,11 +24758,11 @@
       </c>
       <c r="H496" s="51">
         <f t="shared" si="7"/>
-        <v>15.500499999999999</v>
+        <v>16.035</v>
       </c>
       <c r="I496" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J496" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24764,11 +24816,11 @@
       </c>
       <c r="H498" s="51">
         <f t="shared" si="7"/>
-        <v>17.3855</v>
+        <v>17.984999999999999</v>
       </c>
       <c r="I498" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J498" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24909,11 +24961,11 @@
       </c>
       <c r="H503" s="52">
         <f t="shared" si="7"/>
-        <v>15.0655</v>
+        <v>15.585000000000001</v>
       </c>
       <c r="I503" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J503" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24938,11 +24990,11 @@
       </c>
       <c r="H504" s="51">
         <f t="shared" si="7"/>
-        <v>72.211500000000001</v>
+        <v>74.885999999999996</v>
       </c>
       <c r="I504" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925924</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J504" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24967,11 +25019,11 @@
       </c>
       <c r="H505" s="52">
         <f t="shared" si="7"/>
-        <v>21.532499999999999</v>
+        <v>22.274999999999999</v>
       </c>
       <c r="I505" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J505" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -24996,11 +25048,11 @@
       </c>
       <c r="H506" s="51">
         <f t="shared" si="7"/>
-        <v>23.852499999999999</v>
+        <v>24.674999999999997</v>
       </c>
       <c r="I506" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="J506" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -25025,11 +25077,11 @@
       </c>
       <c r="H507" s="52">
         <f t="shared" si="7"/>
-        <v>21.532499999999999</v>
+        <v>22.274999999999999</v>
       </c>
       <c r="I507" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J507" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -25054,11 +25106,11 @@
       </c>
       <c r="H508" s="51">
         <f t="shared" si="7"/>
-        <v>24.142499999999998</v>
+        <v>24.974999999999998</v>
       </c>
       <c r="I508" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J508" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -25083,11 +25135,11 @@
       </c>
       <c r="H509" s="52">
         <f t="shared" si="7"/>
-        <v>19.473499999999998</v>
+        <v>20.145</v>
       </c>
       <c r="I509" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J509" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -25112,11 +25164,11 @@
       </c>
       <c r="H510" s="51">
         <f t="shared" si="7"/>
-        <v>19.473499999999998</v>
+        <v>20.145</v>
       </c>
       <c r="I510" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J510" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -25141,11 +25193,11 @@
       </c>
       <c r="H511" s="52">
         <f t="shared" si="7"/>
-        <v>19.473499999999998</v>
+        <v>20.145</v>
       </c>
       <c r="I511" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J511" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -25170,11 +25222,11 @@
       </c>
       <c r="H512" s="51">
         <f t="shared" si="7"/>
-        <v>19.473499999999998</v>
+        <v>20.145</v>
       </c>
       <c r="I512" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J512" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -25199,11 +25251,11 @@
       </c>
       <c r="H513" s="52">
         <f t="shared" si="7"/>
-        <v>28.449000000000002</v>
+        <v>29.43</v>
       </c>
       <c r="I513" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J513" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -25227,12 +25279,17 @@
         <v>19.62</v>
       </c>
       <c r="H514" s="51">
-        <f t="shared" si="7"/>
-        <v>28.449000000000002</v>
+        <f t="shared" ref="H514:H577" si="8">IF(G514&lt;=5,G514*1.6,
+IF(G514&lt;=10,G514*1.55,
+IF(G514&lt;=25,G514*1.5,
+IF(G514&lt;=50,G514*1.4,
+IF(G514&lt;=100,G514*1.4,
+G514*1.4)))))</f>
+        <v>29.43</v>
       </c>
       <c r="I514" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J514" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -25256,12 +25313,12 @@
         <v>19.62</v>
       </c>
       <c r="H515" s="52">
-        <f t="shared" si="7"/>
-        <v>28.449000000000002</v>
+        <f t="shared" si="8"/>
+        <v>29.43</v>
       </c>
       <c r="I515" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J515" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -25285,12 +25342,12 @@
         <v>74.34</v>
       </c>
       <c r="H516" s="51">
-        <f t="shared" si="7"/>
-        <v>100.35900000000001</v>
+        <f t="shared" si="8"/>
+        <v>104.07599999999999</v>
       </c>
       <c r="I516" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.2592592592592593</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J516" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -25314,7 +25371,7 @@
         <v>29.99</v>
       </c>
       <c r="H517" s="52">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>41.985999999999997</v>
       </c>
       <c r="I517" s="32">
@@ -25343,12 +25400,7 @@
         <v>29.99</v>
       </c>
       <c r="H518" s="51">
-        <f t="shared" ref="H518:H581" si="8">IF(G518&lt;=5,G518*1.6,
-IF(G518&lt;=10,G518*1.55,
-IF(G518&lt;=25,G518*1.45,
-IF(G518&lt;=50,G518*1.4,
-IF(G518&lt;=100,G518*1.35,
-G518*1.333)))))</f>
+        <f t="shared" si="8"/>
         <v>41.985999999999997</v>
       </c>
       <c r="I518" s="34">
@@ -25407,11 +25459,11 @@
       </c>
       <c r="H520" s="51">
         <f t="shared" si="8"/>
-        <v>106.90650000000001</v>
+        <v>110.86599999999999</v>
       </c>
       <c r="I520" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925936</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J520" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -25498,7 +25550,10 @@
       <c r="G523" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H523" s="53"/>
+      <c r="H523" s="53" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I523" s="24"/>
       <c r="J523" s="24"/>
     </row>
@@ -25876,11 +25931,11 @@
       </c>
       <c r="H534" s="51">
         <f t="shared" si="8"/>
-        <v>18.8355</v>
+        <v>19.484999999999999</v>
       </c>
       <c r="I534" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J534" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -25911,11 +25966,11 @@
       </c>
       <c r="H535" s="52">
         <f t="shared" si="8"/>
-        <v>19.560500000000001</v>
+        <v>20.234999999999999</v>
       </c>
       <c r="I535" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J535" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -25981,11 +26036,11 @@
       </c>
       <c r="H537" s="52">
         <f t="shared" si="8"/>
-        <v>15.935499999999999</v>
+        <v>16.484999999999999</v>
       </c>
       <c r="I537" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J537" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -26051,11 +26106,11 @@
       </c>
       <c r="H539" s="52">
         <f t="shared" si="8"/>
-        <v>18.8355</v>
+        <v>19.484999999999999</v>
       </c>
       <c r="I539" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J539" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -26121,11 +26176,11 @@
       </c>
       <c r="H541" s="52">
         <f t="shared" si="8"/>
-        <v>23.185500000000001</v>
+        <v>23.984999999999999</v>
       </c>
       <c r="I541" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J541" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -26191,11 +26246,11 @@
       </c>
       <c r="H543" s="52">
         <f t="shared" si="8"/>
-        <v>21.735499999999998</v>
+        <v>22.484999999999999</v>
       </c>
       <c r="I543" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J543" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -26226,11 +26281,11 @@
       </c>
       <c r="H544" s="51">
         <f t="shared" si="8"/>
-        <v>24.635499999999997</v>
+        <v>25.484999999999999</v>
       </c>
       <c r="I544" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J544" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -26255,11 +26310,11 @@
       </c>
       <c r="H545" s="52">
         <f t="shared" si="8"/>
-        <v>34.060499999999998</v>
+        <v>35.234999999999999</v>
       </c>
       <c r="I545" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J545" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -26284,11 +26339,11 @@
       </c>
       <c r="H546" s="51">
         <f t="shared" si="8"/>
-        <v>16.660499999999999</v>
+        <v>17.234999999999999</v>
       </c>
       <c r="I546" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J546" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -26313,11 +26368,11 @@
       </c>
       <c r="H547" s="52">
         <f t="shared" si="8"/>
-        <v>23.185500000000001</v>
+        <v>23.984999999999999</v>
       </c>
       <c r="I547" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J547" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -26414,7 +26469,10 @@
       <c r="G550" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H550" s="53"/>
+      <c r="H550" s="53" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I550" s="24"/>
       <c r="J550" s="24"/>
     </row>
@@ -26644,7 +26702,10 @@
         <v>9</v>
       </c>
       <c r="G557" s="51"/>
-      <c r="H557" s="52"/>
+      <c r="H557" s="52">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I557" s="32"/>
       <c r="J557" s="32"/>
     </row>
@@ -26664,7 +26725,10 @@
         <v>9</v>
       </c>
       <c r="G558" s="52"/>
-      <c r="H558" s="51"/>
+      <c r="H558" s="51">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I558" s="34"/>
       <c r="J558" s="31"/>
     </row>
@@ -26684,7 +26748,10 @@
         <v>9</v>
       </c>
       <c r="G559" s="51"/>
-      <c r="H559" s="52"/>
+      <c r="H559" s="52">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I559" s="32"/>
       <c r="J559" s="32"/>
     </row>
@@ -26704,7 +26771,10 @@
         <v>9</v>
       </c>
       <c r="G560" s="52"/>
-      <c r="H560" s="51"/>
+      <c r="H560" s="51">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I560" s="34"/>
       <c r="J560" s="31"/>
     </row>
@@ -26728,7 +26798,10 @@
       <c r="G561" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H561" s="53"/>
+      <c r="H561" s="53" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I561" s="24"/>
       <c r="J561" s="24"/>
     </row>
@@ -27102,7 +27175,10 @@
       <c r="G572" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H572" s="53"/>
+      <c r="H572" s="53" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I572" s="24"/>
       <c r="J572" s="24"/>
     </row>
@@ -27130,11 +27206,11 @@
       </c>
       <c r="H573" s="52">
         <f t="shared" si="8"/>
-        <v>18.8355</v>
+        <v>19.484999999999999</v>
       </c>
       <c r="I573" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J573" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -27231,7 +27307,10 @@
       <c r="G576" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H576" s="53"/>
+      <c r="H576" s="53" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I576" s="24"/>
       <c r="J576" s="24"/>
     </row>
@@ -27293,7 +27372,12 @@
         <v>41.29</v>
       </c>
       <c r="H578" s="51">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="H578:H641" si="9">IF(G578&lt;=5,G578*1.6,
+IF(G578&lt;=10,G578*1.55,
+IF(G578&lt;=25,G578*1.5,
+IF(G578&lt;=50,G578*1.4,
+IF(G578&lt;=100,G578*1.4,
+G578*1.4)))))</f>
         <v>57.805999999999997</v>
       </c>
       <c r="I578" s="34">
@@ -27328,12 +27412,12 @@
         <v>17.989999999999998</v>
       </c>
       <c r="H579" s="52">
-        <f t="shared" si="8"/>
-        <v>26.085499999999996</v>
+        <f t="shared" si="9"/>
+        <v>26.984999999999999</v>
       </c>
       <c r="I579" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J579" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -27363,12 +27447,12 @@
         <v>24.99</v>
       </c>
       <c r="H580" s="51">
-        <f t="shared" si="8"/>
-        <v>36.235499999999995</v>
+        <f t="shared" si="9"/>
+        <v>37.484999999999999</v>
       </c>
       <c r="I580" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J580" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -27398,12 +27482,12 @@
         <v>12.99</v>
       </c>
       <c r="H581" s="52">
-        <f t="shared" si="8"/>
-        <v>18.8355</v>
+        <f t="shared" si="9"/>
+        <v>19.484999999999999</v>
       </c>
       <c r="I581" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J581" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -27433,12 +27517,7 @@
         <v>9.9</v>
       </c>
       <c r="H582" s="51">
-        <f t="shared" ref="H582:H645" si="9">IF(G582&lt;=5,G582*1.6,
-IF(G582&lt;=10,G582*1.55,
-IF(G582&lt;=25,G582*1.45,
-IF(G582&lt;=50,G582*1.4,
-IF(G582&lt;=100,G582*1.35,
-G582*1.333)))))</f>
+        <f t="shared" si="9"/>
         <v>15.345000000000001</v>
       </c>
       <c r="I582" s="34">
@@ -27509,11 +27588,11 @@
       </c>
       <c r="H584" s="51">
         <f t="shared" si="9"/>
-        <v>36.25</v>
+        <v>37.5</v>
       </c>
       <c r="I584" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J584" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -27544,11 +27623,11 @@
       </c>
       <c r="H585" s="52">
         <f t="shared" si="9"/>
-        <v>23.620499999999996</v>
+        <v>24.434999999999999</v>
       </c>
       <c r="I585" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J585" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -27579,11 +27658,11 @@
       </c>
       <c r="H586" s="51">
         <f t="shared" si="9"/>
-        <v>28.5505</v>
+        <v>29.535000000000004</v>
       </c>
       <c r="I586" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J586" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -27649,11 +27728,11 @@
       </c>
       <c r="H588" s="51">
         <f t="shared" si="9"/>
-        <v>34.785499999999999</v>
+        <v>35.984999999999999</v>
       </c>
       <c r="I588" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J588" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -27719,11 +27798,11 @@
       </c>
       <c r="H590" s="51">
         <f t="shared" si="9"/>
-        <v>30.435499999999998</v>
+        <v>31.484999999999999</v>
       </c>
       <c r="I590" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J590" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -27748,15 +27827,15 @@
       </c>
       <c r="H591" s="52">
         <f t="shared" si="9"/>
-        <v>146.61667</v>
+        <v>153.98599999999999</v>
       </c>
       <c r="I591" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.24981245311327835</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J591" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
-        <v>REVIEW</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="592" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -27783,11 +27862,11 @@
       </c>
       <c r="H592" s="51">
         <f t="shared" si="9"/>
-        <v>23.620499999999996</v>
+        <v>24.434999999999999</v>
       </c>
       <c r="I592" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J592" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -27818,15 +27897,15 @@
       </c>
       <c r="H593" s="52">
         <f t="shared" si="9"/>
-        <v>266.58667000000003</v>
+        <v>279.98599999999999</v>
       </c>
       <c r="I593" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.24981245311327835</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J593" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
-        <v>REVIEW</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="594" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -27853,11 +27932,11 @@
       </c>
       <c r="H594" s="51">
         <f t="shared" si="9"/>
-        <v>15.935499999999999</v>
+        <v>16.484999999999999</v>
       </c>
       <c r="I594" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J594" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -27888,15 +27967,15 @@
       </c>
       <c r="H595" s="52">
         <f t="shared" si="9"/>
-        <v>162.61266999999998</v>
+        <v>170.78599999999997</v>
       </c>
       <c r="I595" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.24981245311327827</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J595" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
-        <v>REVIEW</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="596" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -27923,11 +28002,11 @@
       </c>
       <c r="H596" s="51">
         <f t="shared" si="9"/>
-        <v>34.4375</v>
+        <v>35.625</v>
       </c>
       <c r="I596" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J596" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -27958,11 +28037,11 @@
       </c>
       <c r="H597" s="52">
         <f t="shared" si="9"/>
-        <v>16.660499999999999</v>
+        <v>17.234999999999999</v>
       </c>
       <c r="I597" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J597" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -27993,11 +28072,11 @@
       </c>
       <c r="H598" s="51">
         <f t="shared" si="9"/>
-        <v>15.935499999999999</v>
+        <v>16.484999999999999</v>
       </c>
       <c r="I598" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J598" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -28232,11 +28311,11 @@
       </c>
       <c r="H605" s="52">
         <f t="shared" si="9"/>
-        <v>23.910499999999995</v>
+        <v>24.734999999999999</v>
       </c>
       <c r="I605" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J605" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -28302,11 +28381,11 @@
       </c>
       <c r="H607" s="52">
         <f t="shared" si="9"/>
-        <v>21.0105</v>
+        <v>21.734999999999999</v>
       </c>
       <c r="I607" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J607" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -28337,11 +28416,11 @@
       </c>
       <c r="H608" s="51">
         <f t="shared" si="9"/>
-        <v>23.185500000000001</v>
+        <v>23.984999999999999</v>
       </c>
       <c r="I608" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J608" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -28407,11 +28486,11 @@
       </c>
       <c r="H610" s="51">
         <f t="shared" si="9"/>
-        <v>27.535499999999995</v>
+        <v>28.484999999999999</v>
       </c>
       <c r="I610" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J610" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -28438,7 +28517,10 @@
       <c r="G611" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H611" s="53"/>
+      <c r="H611" s="53" t="e">
+        <f t="shared" si="9"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I611" s="24"/>
       <c r="J611" s="24"/>
     </row>
@@ -28600,11 +28682,11 @@
       </c>
       <c r="H616" s="51">
         <f t="shared" si="9"/>
-        <v>20.720499999999998</v>
+        <v>21.434999999999999</v>
       </c>
       <c r="I616" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J616" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -28670,11 +28752,11 @@
       </c>
       <c r="H618" s="51">
         <f t="shared" si="9"/>
-        <v>15.2105</v>
+        <v>15.734999999999999</v>
       </c>
       <c r="I618" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J618" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -28839,11 +28921,11 @@
       </c>
       <c r="H623" s="52">
         <f t="shared" si="9"/>
-        <v>23.185500000000001</v>
+        <v>23.984999999999999</v>
       </c>
       <c r="I623" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J623" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -28940,7 +29022,10 @@
       <c r="G626" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H626" s="53"/>
+      <c r="H626" s="53" t="e">
+        <f t="shared" si="9"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I626" s="24"/>
       <c r="J626" s="24"/>
     </row>
@@ -29073,11 +29158,11 @@
       </c>
       <c r="H630" s="51">
         <f t="shared" si="9"/>
-        <v>27.245499999999996</v>
+        <v>28.184999999999999</v>
       </c>
       <c r="I630" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J630" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -29108,11 +29193,11 @@
       </c>
       <c r="H631" s="52">
         <f t="shared" si="9"/>
-        <v>33.335499999999996</v>
+        <v>34.484999999999999</v>
       </c>
       <c r="I631" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J631" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -29141,11 +29226,11 @@
       </c>
       <c r="H632" s="51">
         <f t="shared" si="9"/>
-        <v>16.239999999999998</v>
+        <v>16.799999999999997</v>
       </c>
       <c r="I632" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="J632" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -29176,11 +29261,11 @@
       </c>
       <c r="H633" s="52">
         <f t="shared" si="9"/>
-        <v>23.185500000000001</v>
+        <v>23.984999999999999</v>
       </c>
       <c r="I633" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J633" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -29246,11 +29331,11 @@
       </c>
       <c r="H635" s="52">
         <f t="shared" si="9"/>
-        <v>15.935499999999999</v>
+        <v>16.484999999999999</v>
       </c>
       <c r="I635" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J635" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -29316,11 +29401,11 @@
       </c>
       <c r="H637" s="52">
         <f t="shared" si="9"/>
-        <v>26.085499999999996</v>
+        <v>26.984999999999999</v>
       </c>
       <c r="I637" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J637" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -29415,7 +29500,10 @@
       <c r="G640" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H640" s="53"/>
+      <c r="H640" s="53" t="e">
+        <f t="shared" si="9"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I640" s="24"/>
       <c r="J640" s="24"/>
     </row>
@@ -29469,7 +29557,12 @@
         <v>3.62</v>
       </c>
       <c r="H642" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="H642:H705" si="10">IF(G642&lt;=5,G642*1.6,
+IF(G642&lt;=10,G642*1.55,
+IF(G642&lt;=25,G642*1.5,
+IF(G642&lt;=50,G642*1.4,
+IF(G642&lt;=100,G642*1.4,
+G642*1.4)))))</f>
         <v>5.7920000000000007</v>
       </c>
       <c r="I642" s="34">
@@ -29502,12 +29595,12 @@
         <v>62.99</v>
       </c>
       <c r="H643" s="52">
-        <f t="shared" si="9"/>
-        <v>85.036500000000004</v>
+        <f t="shared" si="10"/>
+        <v>88.185999999999993</v>
       </c>
       <c r="I643" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925924</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J643" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -29535,7 +29628,7 @@
         <v>3.99</v>
       </c>
       <c r="H644" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.3840000000000003</v>
       </c>
       <c r="I644" s="34">
@@ -29568,7 +29661,7 @@
         <v>5.13</v>
       </c>
       <c r="H645" s="52">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.9515000000000002</v>
       </c>
       <c r="I645" s="32">
@@ -29597,12 +29690,7 @@
         <v>29</v>
       </c>
       <c r="H646" s="51">
-        <f t="shared" ref="H646:H709" si="10">IF(G646&lt;=5,G646*1.6,
-IF(G646&lt;=10,G646*1.55,
-IF(G646&lt;=25,G646*1.45,
-IF(G646&lt;=50,G646*1.4,
-IF(G646&lt;=100,G646*1.35,
-G646*1.333)))))</f>
+        <f t="shared" si="10"/>
         <v>40.599999999999994</v>
       </c>
       <c r="I646" s="34">
@@ -29690,11 +29778,11 @@
       </c>
       <c r="H649" s="52">
         <f t="shared" si="10"/>
-        <v>19.574999999999999</v>
+        <v>20.25</v>
       </c>
       <c r="I649" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J649" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -29719,11 +29807,11 @@
       </c>
       <c r="H650" s="51">
         <f t="shared" si="10"/>
-        <v>74.25</v>
+        <v>77</v>
       </c>
       <c r="I650" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925924</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J650" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -30386,11 +30474,11 @@
       </c>
       <c r="H673" s="52">
         <f t="shared" si="10"/>
-        <v>83.7</v>
+        <v>86.8</v>
       </c>
       <c r="I673" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.2592592592592593</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J673" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -30415,11 +30503,11 @@
       </c>
       <c r="H674" s="51">
         <f t="shared" si="10"/>
-        <v>79.650000000000006</v>
+        <v>82.6</v>
       </c>
       <c r="I674" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.2592592592592593</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J674" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -31198,11 +31286,11 @@
       </c>
       <c r="H701" s="52">
         <f t="shared" si="10"/>
-        <v>21.387499999999999</v>
+        <v>22.125</v>
       </c>
       <c r="I701" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J701" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -31342,7 +31430,12 @@
         <v>0.99</v>
       </c>
       <c r="H706" s="51">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="H706:H769" si="11">IF(G706&lt;=5,G706*1.6,
+IF(G706&lt;=10,G706*1.55,
+IF(G706&lt;=25,G706*1.5,
+IF(G706&lt;=50,G706*1.4,
+IF(G706&lt;=100,G706*1.4,
+G706*1.4)))))</f>
         <v>1.5840000000000001</v>
       </c>
       <c r="I706" s="34">
@@ -31371,7 +31464,7 @@
         <v>2.65</v>
       </c>
       <c r="H707" s="52">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.24</v>
       </c>
       <c r="I707" s="32">
@@ -31400,7 +31493,7 @@
         <v>3.16</v>
       </c>
       <c r="H708" s="51">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.0560000000000009</v>
       </c>
       <c r="I708" s="34">
@@ -31429,7 +31522,7 @@
         <v>2.56</v>
       </c>
       <c r="H709" s="52">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.0960000000000001</v>
       </c>
       <c r="I709" s="32">
@@ -31458,12 +31551,7 @@
         <v>3.77</v>
       </c>
       <c r="H710" s="51">
-        <f t="shared" ref="H710:H772" si="11">IF(G710&lt;=5,G710*1.6,
-IF(G710&lt;=10,G710*1.55,
-IF(G710&lt;=25,G710*1.45,
-IF(G710&lt;=50,G710*1.4,
-IF(G710&lt;=100,G710*1.35,
-G710*1.333)))))</f>
+        <f t="shared" si="11"/>
         <v>6.032</v>
       </c>
       <c r="I710" s="34">
@@ -31638,11 +31726,11 @@
       </c>
       <c r="H716" s="51">
         <f t="shared" si="11"/>
-        <v>19.574999999999999</v>
+        <v>20.25</v>
       </c>
       <c r="I716" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J716" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -31667,11 +31755,11 @@
       </c>
       <c r="H717" s="52">
         <f t="shared" si="11"/>
-        <v>20.3</v>
+        <v>21</v>
       </c>
       <c r="I717" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J717" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -32005,7 +32093,10 @@
       <c r="E729" s="2"/>
       <c r="F729" s="2"/>
       <c r="G729" s="53"/>
-      <c r="H729" s="53"/>
+      <c r="H729" s="53">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="I729" s="24"/>
       <c r="J729" s="24"/>
     </row>
@@ -32033,11 +32124,11 @@
       </c>
       <c r="H730" s="51">
         <f t="shared" si="11"/>
-        <v>27.912499999999998</v>
+        <v>28.875</v>
       </c>
       <c r="I730" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J730" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -32068,11 +32159,11 @@
       </c>
       <c r="H731" s="52">
         <f t="shared" si="11"/>
-        <v>93.136499999999998</v>
+        <v>96.585999999999984</v>
       </c>
       <c r="I731" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.2592592592592593</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J731" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -32173,11 +32264,11 @@
       </c>
       <c r="H734" s="51">
         <f t="shared" si="11"/>
-        <v>34.292499999999997</v>
+        <v>35.474999999999994</v>
       </c>
       <c r="I734" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="J734" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -32208,11 +32299,11 @@
       </c>
       <c r="H735" s="52">
         <f t="shared" si="11"/>
-        <v>28.260499999999997</v>
+        <v>29.234999999999999</v>
       </c>
       <c r="I735" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J735" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -32239,11 +32330,11 @@
       </c>
       <c r="H736" s="51">
         <f t="shared" si="11"/>
-        <v>19.574999999999999</v>
+        <v>20.25</v>
       </c>
       <c r="I736" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J736" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -32270,11 +32361,11 @@
       </c>
       <c r="H737" s="52">
         <f t="shared" si="11"/>
-        <v>15.920999999999999</v>
+        <v>16.47</v>
       </c>
       <c r="I737" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="J737" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -32299,11 +32390,11 @@
       </c>
       <c r="H738" s="51">
         <f t="shared" si="11"/>
-        <v>31.392499999999998</v>
+        <v>32.474999999999994</v>
       </c>
       <c r="I738" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="J738" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -32392,11 +32483,11 @@
       </c>
       <c r="H741" s="52">
         <f t="shared" si="11"/>
-        <v>22.170499999999997</v>
+        <v>22.934999999999999</v>
       </c>
       <c r="I741" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J741" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -32454,7 +32545,10 @@
       <c r="G743" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H743" s="53"/>
+      <c r="H743" s="53" t="e">
+        <f t="shared" si="11"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I743" s="24"/>
       <c r="J743" s="24"/>
     </row>
@@ -32583,7 +32677,10 @@
       <c r="G747" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H747" s="53"/>
+      <c r="H747" s="53" t="e">
+        <f t="shared" si="11"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I747" s="24"/>
       <c r="J747" s="24"/>
     </row>
@@ -32611,11 +32708,11 @@
       </c>
       <c r="H748" s="51">
         <f t="shared" si="11"/>
-        <v>18.8355</v>
+        <v>19.484999999999999</v>
       </c>
       <c r="I748" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J748" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -32646,11 +32743,11 @@
       </c>
       <c r="H749" s="52">
         <f t="shared" si="11"/>
-        <v>28.260499999999997</v>
+        <v>29.234999999999999</v>
       </c>
       <c r="I749" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J749" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -32681,11 +32778,11 @@
       </c>
       <c r="H750" s="51">
         <f t="shared" si="11"/>
-        <v>70.186500000000009</v>
+        <v>72.786000000000001</v>
       </c>
       <c r="I750" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.25925925925925936</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J750" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -32716,11 +32813,11 @@
       </c>
       <c r="H751" s="52">
         <f t="shared" si="11"/>
-        <v>19.9375</v>
+        <v>20.625</v>
       </c>
       <c r="I751" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J751" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -32751,11 +32848,11 @@
       </c>
       <c r="H752" s="51">
         <f t="shared" si="11"/>
-        <v>24.65</v>
+        <v>25.5</v>
       </c>
       <c r="I752" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J752" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -32856,11 +32953,11 @@
       </c>
       <c r="H755" s="52">
         <f t="shared" si="11"/>
-        <v>15.007499999999999</v>
+        <v>15.524999999999999</v>
       </c>
       <c r="I755" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J755" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -32891,11 +32988,11 @@
       </c>
       <c r="H756" s="51">
         <f t="shared" si="11"/>
-        <v>20.285499999999999</v>
+        <v>20.984999999999999</v>
       </c>
       <c r="I756" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J756" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -32926,11 +33023,11 @@
       </c>
       <c r="H757" s="52">
         <f t="shared" si="11"/>
-        <v>22.547499999999999</v>
+        <v>23.325000000000003</v>
       </c>
       <c r="I757" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J757" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -32990,11 +33087,11 @@
       </c>
       <c r="H759" s="52">
         <f t="shared" si="11"/>
-        <v>22.547499999999999</v>
+        <v>23.325000000000003</v>
       </c>
       <c r="I759" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J759" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -33060,11 +33157,11 @@
       </c>
       <c r="H761" s="52">
         <f t="shared" si="11"/>
-        <v>15.2105</v>
+        <v>15.734999999999999</v>
       </c>
       <c r="I761" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J761" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -33091,7 +33188,10 @@
       <c r="G762" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H762" s="53"/>
+      <c r="H762" s="53" t="e">
+        <f t="shared" si="11"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I762" s="24"/>
       <c r="J762" s="24"/>
     </row>
@@ -33325,7 +33425,10 @@
       <c r="G769" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H769" s="53"/>
+      <c r="H769" s="53" t="e">
+        <f t="shared" si="11"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I769" s="24"/>
       <c r="J769" s="24"/>
     </row>
@@ -33352,12 +33455,17 @@
         <v>10.99</v>
       </c>
       <c r="H770" s="51">
-        <f t="shared" si="11"/>
-        <v>15.935499999999999</v>
+        <f t="shared" ref="H770:H833" si="12">IF(G770&lt;=5,G770*1.6,
+IF(G770&lt;=10,G770*1.55,
+IF(G770&lt;=25,G770*1.5,
+IF(G770&lt;=50,G770*1.4,
+IF(G770&lt;=100,G770*1.4,
+G770*1.4)))))</f>
+        <v>16.484999999999999</v>
       </c>
       <c r="I770" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J770" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -33387,7 +33495,7 @@
         <v>2.99</v>
       </c>
       <c r="H771" s="52">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.7840000000000007</v>
       </c>
       <c r="I771" s="32">
@@ -33422,7 +33530,7 @@
         <v>9.0500000000000007</v>
       </c>
       <c r="H772" s="51">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>14.027500000000002</v>
       </c>
       <c r="I772" s="34">
@@ -33454,7 +33562,10 @@
       <c r="G773" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H773" s="53"/>
+      <c r="H773" s="53" t="e">
+        <f t="shared" si="12"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I773" s="24"/>
       <c r="J773" s="24"/>
     </row>
@@ -33481,12 +33592,7 @@
         <v>29.99</v>
       </c>
       <c r="H774" s="51">
-        <f t="shared" ref="H774:H836" si="12">IF(G774&lt;=5,G774*1.6,
-IF(G774&lt;=10,G774*1.55,
-IF(G774&lt;=25,G774*1.45,
-IF(G774&lt;=50,G774*1.4,
-IF(G774&lt;=100,G774*1.35,
-G774*1.333)))))</f>
+        <f t="shared" si="12"/>
         <v>41.985999999999997</v>
       </c>
       <c r="I774" s="34">
@@ -33623,7 +33729,10 @@
       <c r="G778" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H778" s="53"/>
+      <c r="H778" s="53" t="e">
+        <f t="shared" si="12"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I778" s="24"/>
       <c r="J778" s="24"/>
     </row>
@@ -33756,11 +33865,11 @@
       </c>
       <c r="H782" s="51">
         <f t="shared" si="12"/>
-        <v>24.635499999999997</v>
+        <v>25.484999999999999</v>
       </c>
       <c r="I782" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J782" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -33791,11 +33900,11 @@
       </c>
       <c r="H783" s="52">
         <f t="shared" si="12"/>
-        <v>18.8355</v>
+        <v>19.484999999999999</v>
       </c>
       <c r="I783" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J783" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -33861,11 +33970,11 @@
       </c>
       <c r="H785" s="52">
         <f t="shared" si="12"/>
-        <v>15.935499999999999</v>
+        <v>16.484999999999999</v>
       </c>
       <c r="I785" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J785" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -33931,11 +34040,11 @@
       </c>
       <c r="H787" s="52">
         <f t="shared" si="12"/>
-        <v>15.935499999999999</v>
+        <v>16.484999999999999</v>
       </c>
       <c r="I787" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J787" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -34137,7 +34246,10 @@
       <c r="G793" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H793" s="53"/>
+      <c r="H793" s="53" t="e">
+        <f t="shared" si="12"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I793" s="24"/>
       <c r="J793" s="24"/>
     </row>
@@ -34165,11 +34277,11 @@
       </c>
       <c r="H794" s="51">
         <f t="shared" si="12"/>
-        <v>17.3855</v>
+        <v>17.984999999999999</v>
       </c>
       <c r="I794" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J794" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -34231,7 +34343,10 @@
       <c r="G796" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H796" s="53"/>
+      <c r="H796" s="53" t="e">
+        <f t="shared" si="12"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I796" s="24"/>
       <c r="J796" s="24"/>
     </row>
@@ -34432,11 +34547,11 @@
       </c>
       <c r="H802" s="52">
         <f t="shared" si="12"/>
-        <v>19.560500000000001</v>
+        <v>20.234999999999999</v>
       </c>
       <c r="I802" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J802" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -34502,11 +34617,11 @@
       </c>
       <c r="H804" s="52">
         <f t="shared" si="12"/>
-        <v>26.085499999999996</v>
+        <v>26.984999999999999</v>
       </c>
       <c r="I804" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J804" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -34533,7 +34648,10 @@
       <c r="G805" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H805" s="53"/>
+      <c r="H805" s="53" t="e">
+        <f t="shared" si="12"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I805" s="24"/>
       <c r="J805" s="24"/>
     </row>
@@ -34631,11 +34749,11 @@
       </c>
       <c r="H808" s="52">
         <f t="shared" si="12"/>
-        <v>19.343</v>
+        <v>20.009999999999998</v>
       </c>
       <c r="I808" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="J808" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -34771,11 +34889,11 @@
       </c>
       <c r="H812" s="52">
         <f t="shared" si="12"/>
-        <v>15.225</v>
+        <v>15.75</v>
       </c>
       <c r="I812" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J812" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -34841,11 +34959,11 @@
       </c>
       <c r="H814" s="52">
         <f t="shared" si="12"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I814" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J814" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -34876,11 +34994,11 @@
       </c>
       <c r="H815" s="51">
         <f t="shared" si="12"/>
-        <v>20.227499999999999</v>
+        <v>20.924999999999997</v>
       </c>
       <c r="I815" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="J815" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -34911,11 +35029,11 @@
       </c>
       <c r="H816" s="52">
         <f t="shared" si="12"/>
-        <v>20.3</v>
+        <v>21</v>
       </c>
       <c r="I816" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J816" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -34946,11 +35064,11 @@
       </c>
       <c r="H817" s="51">
         <f t="shared" si="12"/>
-        <v>24.186</v>
+        <v>25.02</v>
       </c>
       <c r="I817" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J817" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -34981,11 +35099,11 @@
       </c>
       <c r="H818" s="52">
         <f t="shared" si="12"/>
-        <v>26.099999999999998</v>
+        <v>27</v>
       </c>
       <c r="I818" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J818" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -35016,11 +35134,11 @@
       </c>
       <c r="H819" s="51">
         <f t="shared" si="12"/>
-        <v>26.099999999999998</v>
+        <v>27</v>
       </c>
       <c r="I819" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J819" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -35051,11 +35169,11 @@
       </c>
       <c r="H820" s="52">
         <f t="shared" si="12"/>
-        <v>26.099999999999998</v>
+        <v>27</v>
       </c>
       <c r="I820" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J820" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -35121,11 +35239,11 @@
       </c>
       <c r="H822" s="52">
         <f t="shared" si="12"/>
-        <v>20.3</v>
+        <v>21</v>
       </c>
       <c r="I822" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J822" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -35226,11 +35344,11 @@
       </c>
       <c r="H825" s="51">
         <f t="shared" si="12"/>
-        <v>31.9</v>
+        <v>33</v>
       </c>
       <c r="I825" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J825" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -35296,11 +35414,11 @@
       </c>
       <c r="H827" s="51">
         <f t="shared" si="12"/>
-        <v>15.935499999999999</v>
+        <v>16.484999999999999</v>
       </c>
       <c r="I827" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J827" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -35436,11 +35554,11 @@
       </c>
       <c r="H831" s="51">
         <f t="shared" si="12"/>
-        <v>21.75</v>
+        <v>22.5</v>
       </c>
       <c r="I831" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J831" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -35471,11 +35589,11 @@
       </c>
       <c r="H832" s="52">
         <f t="shared" si="12"/>
-        <v>31.9</v>
+        <v>33</v>
       </c>
       <c r="I832" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J832" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -35540,12 +35658,17 @@
         <v>18</v>
       </c>
       <c r="H834" s="52">
-        <f t="shared" si="12"/>
-        <v>26.099999999999998</v>
+        <f t="shared" ref="H834:H897" si="13">IF(G834&lt;=5,G834*1.6,
+IF(G834&lt;=10,G834*1.55,
+IF(G834&lt;=25,G834*1.5,
+IF(G834&lt;=50,G834*1.4,
+IF(G834&lt;=100,G834*1.4,
+G834*1.4)))))</f>
+        <v>27</v>
       </c>
       <c r="I834" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J834" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -35575,7 +35698,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H835" s="51">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.3599999999999994</v>
       </c>
       <c r="I835" s="34">
@@ -35610,7 +35733,7 @@
         <v>8</v>
       </c>
       <c r="H836" s="52">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>12.4</v>
       </c>
       <c r="I836" s="32">
@@ -35645,12 +35768,7 @@
         <v>6.99</v>
       </c>
       <c r="H837" s="51">
-        <f t="shared" ref="H837:H900" si="13">IF(G837&lt;=5,G837*1.6,
-IF(G837&lt;=10,G837*1.55,
-IF(G837&lt;=25,G837*1.45,
-IF(G837&lt;=50,G837*1.4,
-IF(G837&lt;=100,G837*1.35,
-G837*1.333)))))</f>
+        <f t="shared" si="13"/>
         <v>10.8345</v>
       </c>
       <c r="I837" s="34">
@@ -35787,11 +35905,11 @@
       </c>
       <c r="H841" s="51">
         <f t="shared" si="13"/>
-        <v>14.79</v>
+        <v>15.299999999999999</v>
       </c>
       <c r="I841" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J841" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -35822,11 +35940,11 @@
       </c>
       <c r="H842" s="52">
         <f t="shared" si="13"/>
-        <v>20.3</v>
+        <v>21</v>
       </c>
       <c r="I842" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J842" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -35857,11 +35975,11 @@
       </c>
       <c r="H843" s="51">
         <f t="shared" si="13"/>
-        <v>31.9</v>
+        <v>33</v>
       </c>
       <c r="I843" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J843" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -35927,11 +36045,11 @@
       </c>
       <c r="H845" s="51">
         <f t="shared" si="13"/>
-        <v>31.9</v>
+        <v>33</v>
       </c>
       <c r="I845" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J845" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -36172,11 +36290,11 @@
       </c>
       <c r="H852" s="52">
         <f t="shared" si="13"/>
-        <v>17.3855</v>
+        <v>17.984999999999999</v>
       </c>
       <c r="I852" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J852" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -36207,11 +36325,11 @@
       </c>
       <c r="H853" s="51">
         <f t="shared" si="13"/>
-        <v>17.3855</v>
+        <v>17.984999999999999</v>
       </c>
       <c r="I853" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J853" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -36487,11 +36605,11 @@
       </c>
       <c r="H861" s="51">
         <f t="shared" si="13"/>
-        <v>26.099999999999998</v>
+        <v>27</v>
       </c>
       <c r="I861" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J861" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -36732,11 +36850,11 @@
       </c>
       <c r="H868" s="52">
         <f t="shared" si="13"/>
-        <v>36.25</v>
+        <v>37.5</v>
       </c>
       <c r="I868" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J868" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -36767,11 +36885,11 @@
       </c>
       <c r="H869" s="51">
         <f t="shared" si="13"/>
-        <v>19.574999999999999</v>
+        <v>20.25</v>
       </c>
       <c r="I869" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J869" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -37008,7 +37126,10 @@
       <c r="G876" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H876" s="53"/>
+      <c r="H876" s="53" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="I876" s="24"/>
       <c r="J876" s="24"/>
     </row>
@@ -37141,11 +37262,11 @@
       </c>
       <c r="H880" s="52">
         <f t="shared" si="13"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I880" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J880" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -37211,11 +37332,11 @@
       </c>
       <c r="H882" s="52">
         <f t="shared" si="13"/>
-        <v>27.114999999999998</v>
+        <v>28.049999999999997</v>
       </c>
       <c r="I882" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J882" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -37281,11 +37402,11 @@
       </c>
       <c r="H884" s="52">
         <f t="shared" si="13"/>
-        <v>36.25</v>
+        <v>37.5</v>
       </c>
       <c r="I884" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J884" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -37316,11 +37437,11 @@
       </c>
       <c r="H885" s="51">
         <f t="shared" si="13"/>
-        <v>36.25</v>
+        <v>37.5</v>
       </c>
       <c r="I885" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J885" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -37351,11 +37472,11 @@
       </c>
       <c r="H886" s="52">
         <f t="shared" si="13"/>
-        <v>36.25</v>
+        <v>37.5</v>
       </c>
       <c r="I886" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J886" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -37386,11 +37507,11 @@
       </c>
       <c r="H887" s="51">
         <f t="shared" si="13"/>
-        <v>26.099999999999998</v>
+        <v>27</v>
       </c>
       <c r="I887" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J887" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -37421,11 +37542,11 @@
       </c>
       <c r="H888" s="52">
         <f t="shared" si="13"/>
-        <v>26.099999999999998</v>
+        <v>27</v>
       </c>
       <c r="I888" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J888" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -37456,11 +37577,11 @@
       </c>
       <c r="H889" s="51">
         <f t="shared" si="13"/>
-        <v>36.25</v>
+        <v>37.5</v>
       </c>
       <c r="I889" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J889" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -37491,11 +37612,11 @@
       </c>
       <c r="H890" s="52">
         <f t="shared" si="13"/>
-        <v>20.3</v>
+        <v>21</v>
       </c>
       <c r="I890" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J890" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -37526,11 +37647,11 @@
       </c>
       <c r="H891" s="51">
         <f t="shared" si="13"/>
-        <v>34.799999999999997</v>
+        <v>36</v>
       </c>
       <c r="I891" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J891" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -37561,11 +37682,11 @@
       </c>
       <c r="H892" s="52">
         <f t="shared" si="13"/>
-        <v>26.099999999999998</v>
+        <v>27</v>
       </c>
       <c r="I892" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J892" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -37631,11 +37752,11 @@
       </c>
       <c r="H894" s="52">
         <f t="shared" si="13"/>
-        <v>34.799999999999997</v>
+        <v>36</v>
       </c>
       <c r="I894" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J894" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -37666,11 +37787,11 @@
       </c>
       <c r="H895" s="51">
         <f t="shared" si="13"/>
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="I895" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J895" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -37701,11 +37822,11 @@
       </c>
       <c r="H896" s="52">
         <f t="shared" si="13"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I896" s="32">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J896" s="32" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -37736,11 +37857,11 @@
       </c>
       <c r="H897" s="51">
         <f t="shared" si="13"/>
-        <v>26.099999999999998</v>
+        <v>27</v>
       </c>
       <c r="I897" s="34">
         <f>(Table1[[#This Row],[SALE PRICE]]-Table1[[#This Row],[COST PRICE]])/Table1[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J897" s="31" t="str">
         <f>IF(Table1[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -37770,7 +37891,12 @@
         <v>4.75</v>
       </c>
       <c r="H898" s="52">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="H898:H961" si="14">IF(G898&lt;=5,G898*1.6,
+IF(G898&lt;=10,G898*1.55,
+IF(G898&lt;=25,G898*1.5,
+IF(G898&lt;=50,G898*1.4,
+IF(G898&lt;=100,G898*1.4,
+G898*1.4)))))</f>
         <v>7.6000000000000005</v>
       </c>
       <c r="I898" s="32">
@@ -37805,7 +37931,7 @@
         <v>27.49</v>
       </c>
       <c r="H899" s="51">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>38.485999999999997</v>
       </c>
       <c r="I899" s="34">
@@ -37836,7 +37962,7 @@
         <v>10</v>
       </c>
       <c r="H900" s="51">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>15.5</v>
       </c>
       <c r="I900" s="32">
@@ -37867,12 +37993,7 @@
         <v>4.8</v>
       </c>
       <c r="H901" s="54">
-        <f t="shared" ref="H901" si="14">IF(G901&lt;=5,G901*1.6,
-IF(G901&lt;=10,G901*1.55,
-IF(G901&lt;=25,G901*1.45,
-IF(G901&lt;=50,G901*1.4,
-IF(G901&lt;=100,G901*1.35,
-G901*1.333)))))</f>
+        <f t="shared" si="14"/>
         <v>7.68</v>
       </c>
       <c r="I901" s="34">
@@ -37945,12 +38066,12 @@
         <v>0.99</v>
       </c>
       <c r="H904" s="51">
-        <f>IF(G904&lt;=5,G904*1.6,
+        <f t="shared" ref="H904:H967" si="15">IF(G904&lt;=5,G904*1.6,
 IF(G904&lt;=10,G904*1.55,
-IF(G904&lt;=25,G904*1.45,
+IF(G904&lt;=25,G904*1.5,
 IF(G904&lt;=50,G904*1.4,
-IF(G904&lt;=100,G904*1.35,
-G904*1.333)))))</f>
+IF(G904&lt;=100,G904*1.4,
+G904*1.4)))))</f>
         <v>1.5840000000000001</v>
       </c>
       <c r="I904" s="34">
@@ -37979,12 +38100,7 @@
         <v>1.19</v>
       </c>
       <c r="H905" s="52">
-        <f t="shared" ref="H905:H968" si="15">IF(G905&lt;=5,G905*1.6,
-IF(G905&lt;=10,G905*1.55,
-IF(G905&lt;=25,G905*1.45,
-IF(G905&lt;=50,G905*1.4,
-IF(G905&lt;=100,G905*1.35,
-G905*1.333)))))</f>
+        <f t="shared" si="15"/>
         <v>1.9039999999999999</v>
       </c>
       <c r="I905" s="48">
@@ -38129,12 +38245,7 @@
         <v>3.19</v>
       </c>
       <c r="H910" s="51">
-        <f>IF(G910&lt;=5,G910*1.6,
-IF(G910&lt;=10,G910*1.55,
-IF(G910&lt;=25,G910*1.45,
-IF(G910&lt;=50,G910*1.4,
-IF(G910&lt;=100,G910*1.35,
-G910*1.333)))))</f>
+        <f t="shared" si="15"/>
         <v>5.1040000000000001</v>
       </c>
       <c r="I910" s="34">
@@ -39816,7 +39927,12 @@
         <v>1.39</v>
       </c>
       <c r="H968" s="51">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="H968:H1031" si="16">IF(G968&lt;=5,G968*1.6,
+IF(G968&lt;=10,G968*1.55,
+IF(G968&lt;=25,G968*1.5,
+IF(G968&lt;=50,G968*1.4,
+IF(G968&lt;=100,G968*1.4,
+G968*1.4)))))</f>
         <v>2.2239999999999998</v>
       </c>
       <c r="I968" s="34">
@@ -39845,12 +39961,7 @@
         <v>1.99</v>
       </c>
       <c r="H969" s="52">
-        <f t="shared" ref="H969:H1032" si="16">IF(G969&lt;=5,G969*1.6,
-IF(G969&lt;=10,G969*1.55,
-IF(G969&lt;=25,G969*1.45,
-IF(G969&lt;=50,G969*1.4,
-IF(G969&lt;=100,G969*1.35,
-G969*1.333)))))</f>
+        <f t="shared" si="16"/>
         <v>3.1840000000000002</v>
       </c>
       <c r="I969" s="48">
@@ -40518,11 +40629,11 @@
       </c>
       <c r="H992" s="52">
         <f t="shared" si="16"/>
-        <v>36.235499999999995</v>
+        <v>37.484999999999999</v>
       </c>
       <c r="I992" s="34">
         <f>(Table4[[#This Row],[SALE PRICE]]-Table4[[#This Row],[COST PRICE]])/Table4[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620685</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="J992" s="31" t="str">
         <f>IF(Table4[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -41065,11 +41176,11 @@
       </c>
       <c r="H1011" s="52">
         <f t="shared" si="16"/>
-        <v>17.3855</v>
+        <v>17.984999999999999</v>
       </c>
       <c r="I1011" s="48">
         <f>(Table4[[#This Row],[SALE PRICE]]-Table4[[#This Row],[COST PRICE]])/Table4[[#This Row],[SALE PRICE]]</f>
-        <v>0.31034482758620691</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J1011" s="31" t="str">
         <f>IF(Table4[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
@@ -41595,7 +41706,12 @@
       <c r="F1032" s="17"/>
       <c r="G1032" s="51"/>
       <c r="H1032" s="52">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="H1032:H1095" si="17">IF(G1032&lt;=5,G1032*1.6,
+IF(G1032&lt;=10,G1032*1.55,
+IF(G1032&lt;=25,G1032*1.5,
+IF(G1032&lt;=50,G1032*1.4,
+IF(G1032&lt;=100,G1032*1.4,
+G1032*1.4)))))</f>
         <v>0</v>
       </c>
       <c r="I1032" s="34" t="e">
@@ -41618,12 +41734,7 @@
       <c r="F1033" s="18"/>
       <c r="G1033" s="52"/>
       <c r="H1033" s="52">
-        <f t="shared" ref="H1033:H1096" si="17">IF(G1033&lt;=5,G1033*1.6,
-IF(G1033&lt;=10,G1033*1.55,
-IF(G1033&lt;=25,G1033*1.45,
-IF(G1033&lt;=50,G1033*1.4,
-IF(G1033&lt;=100,G1033*1.35,
-G1033*1.333)))))</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="I1033" s="48" t="e">
@@ -41980,7 +42091,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="1049" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1049" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1049" s="58" t="s">
         <v>0</v>
       </c>
@@ -42002,8 +42113,9 @@
       <c r="G1049" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="H1049" s="60" t="s">
-        <v>6</v>
+      <c r="H1049" s="60" t="e">
+        <f t="shared" si="17"/>
+        <v>#VALUE!</v>
       </c>
       <c r="I1049" s="61" t="s">
         <v>1929</v>
@@ -42012,7 +42124,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="1050" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1050" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1050" s="18" t="s">
         <v>2195</v>
       </c>
@@ -42041,7 +42153,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="1051" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1051" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1051" s="29" t="s">
         <v>2196</v>
       </c>
@@ -42070,7 +42182,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="1052" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1052" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1052" s="18" t="s">
         <v>2197</v>
       </c>
@@ -42099,7 +42211,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="1053" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1053" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1053" s="29" t="s">
         <v>2198</v>
       </c>
@@ -42128,7 +42240,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="1054" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1054" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1054" s="18" t="s">
         <v>2199</v>
       </c>
@@ -42157,7 +42269,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="1055" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1055" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1055" s="29" t="s">
         <v>2200</v>
       </c>
@@ -42180,7 +42292,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="1056" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1056" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1056" s="18" t="s">
         <v>2201</v>
       </c>
@@ -42203,7 +42315,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="1057" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1057" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1057" s="29" t="s">
         <v>2202</v>
       </c>
@@ -42226,7 +42338,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="1058" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1058" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1058" s="18" t="s">
         <v>2203</v>
       </c>
@@ -42249,7 +42361,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="1059" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1059" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1059" s="29" t="s">
         <v>2204</v>
       </c>
@@ -42272,7 +42384,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="1060" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1060" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1060" s="18" t="s">
         <v>2205</v>
       </c>
@@ -42295,7 +42407,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="1061" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1061" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1061" s="29" t="s">
         <v>2206</v>
       </c>
@@ -42318,7 +42430,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="1062" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1062" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1062" s="18" t="s">
         <v>2207</v>
       </c>
@@ -42341,7 +42453,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="1063" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1063" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1063" s="29" t="s">
         <v>2208</v>
       </c>
@@ -42364,7 +42476,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="1064" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1064" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1064" s="18" t="s">
         <v>2209</v>
       </c>
@@ -42387,7 +42499,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="1065" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1065" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1065" s="29" t="s">
         <v>2210</v>
       </c>
@@ -42410,7 +42522,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="1066" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1066" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1066" s="18" t="s">
         <v>2211</v>
       </c>
@@ -42433,7 +42545,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="1067" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1067" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1067" s="29" t="s">
         <v>2212</v>
       </c>
@@ -42456,7 +42568,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="1068" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1068" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1068" s="18" t="s">
         <v>2213</v>
       </c>
@@ -42479,7 +42591,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="1069" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1069" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1069" s="29" t="s">
         <v>2214</v>
       </c>
@@ -42502,7 +42614,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="1070" spans="1:10" s="63" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1070" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1070" s="18" t="s">
         <v>2215</v>
       </c>
@@ -43111,7 +43223,12 @@
       <c r="F1096" s="18"/>
       <c r="G1096" s="52"/>
       <c r="H1096" s="56">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="H1096:H1159" si="18">IF(G1096&lt;=5,G1096*1.6,
+IF(G1096&lt;=10,G1096*1.55,
+IF(G1096&lt;=25,G1096*1.5,
+IF(G1096&lt;=50,G1096*1.4,
+IF(G1096&lt;=100,G1096*1.4,
+G1096*1.4)))))</f>
         <v>0</v>
       </c>
       <c r="I1096" s="49" t="e">
@@ -43134,12 +43251,7 @@
       <c r="F1097" s="29"/>
       <c r="G1097" s="54"/>
       <c r="H1097" s="57">
-        <f t="shared" ref="H1097:H1135" si="18">IF(G1097&lt;=5,G1097*1.6,
-IF(G1097&lt;=10,G1097*1.55,
-IF(G1097&lt;=25,G1097*1.45,
-IF(G1097&lt;=50,G1097*1.4,
-IF(G1097&lt;=100,G1097*1.35,
-G1097*1.333)))))</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="I1097" s="50" t="e">
@@ -43717,15 +43829,15 @@
       </c>
       <c r="H1122" s="56">
         <f t="shared" si="18"/>
-        <v>135.73938999999999</v>
+        <v>142.56199999999998</v>
       </c>
       <c r="I1122" s="49">
         <f>(Table4[[#This Row],[SALE PRICE]]-Table4[[#This Row],[COST PRICE]])/Table4[[#This Row],[SALE PRICE]]</f>
-        <v>0.24981245311327827</v>
+        <v>0.28571428571428564</v>
       </c>
       <c r="J1122" s="18" t="str">
         <f>IF(Table4[[#This Row],[MARGIN]]&lt;25%, "REVIEW", "OK")</f>
-        <v>REVIEW</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="1123" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -44090,7 +44202,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="63" t="s">
         <v>1123</v>
       </c>
       <c r="B2" s="19" t="s">
